--- a/java/verify/fixtures/空列词表全量（ods_t_name_words）.xlsx
+++ b/java/verify/fixtures/空列词表全量（ods_t_name_words）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ANS1"/>
+  <dimension ref="A1:AOI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1774,3940 +1774,4020 @@
       </c>
       <c r="JL1" t="inlineStr">
         <is>
+          <t>有效期</t>
+        </is>
+      </c>
+      <c r="JM1" t="inlineStr">
+        <is>
+          <t>到期</t>
+        </is>
+      </c>
+      <c r="JN1" t="inlineStr">
+        <is>
           <t>时长</t>
         </is>
       </c>
-      <c r="JM1" t="inlineStr">
+      <c r="JO1" t="inlineStr">
         <is>
           <t>工期</t>
         </is>
       </c>
-      <c r="JN1" t="inlineStr">
+      <c r="JP1" t="inlineStr">
         <is>
           <t>周期</t>
         </is>
       </c>
-      <c r="JO1" t="inlineStr">
+      <c r="JQ1" t="inlineStr">
         <is>
           <t>耗时</t>
         </is>
       </c>
-      <c r="JP1" t="inlineStr">
+      <c r="JR1" t="inlineStr">
         <is>
           <t>用时</t>
         </is>
       </c>
-      <c r="JQ1" t="inlineStr">
+      <c r="JS1" t="inlineStr">
         <is>
           <t>间隔</t>
         </is>
       </c>
-      <c r="JR1" t="inlineStr">
+      <c r="JT1" t="inlineStr">
         <is>
           <t>续航</t>
         </is>
       </c>
-      <c r="JS1" t="inlineStr">
+      <c r="JU1" t="inlineStr">
         <is>
           <t>时延</t>
         </is>
       </c>
-      <c r="JT1" t="inlineStr">
+      <c r="JV1" t="inlineStr">
         <is>
           <t>延时</t>
         </is>
       </c>
-      <c r="JU1" t="inlineStr">
+      <c r="JW1" t="inlineStr">
         <is>
           <t>工时</t>
         </is>
       </c>
-      <c r="JV1" t="inlineStr">
+      <c r="JX1" t="inlineStr">
         <is>
           <t>机时</t>
         </is>
       </c>
-      <c r="JW1" t="inlineStr">
+      <c r="JY1" t="inlineStr">
         <is>
           <t>台时</t>
         </is>
       </c>
-      <c r="JX1" t="inlineStr">
+      <c r="JZ1" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="JY1" t="inlineStr">
+      <c r="KA1" t="inlineStr">
         <is>
           <t>个数</t>
         </is>
       </c>
-      <c r="JZ1" t="inlineStr">
+      <c r="KB1" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="KA1" t="inlineStr">
+      <c r="KC1" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="KB1" t="inlineStr">
+      <c r="KD1" t="inlineStr">
         <is>
           <t>库存</t>
         </is>
       </c>
-      <c r="KC1" t="inlineStr">
+      <c r="KE1" t="inlineStr">
         <is>
           <t>张数</t>
         </is>
       </c>
-      <c r="KD1" t="inlineStr">
+      <c r="KF1" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="KE1" t="inlineStr">
+      <c r="KG1" t="inlineStr">
         <is>
           <t>台数</t>
         </is>
       </c>
-      <c r="KF1" t="inlineStr">
+      <c r="KH1" t="inlineStr">
         <is>
           <t>点数</t>
         </is>
       </c>
-      <c r="KG1" t="inlineStr">
+      <c r="KI1" t="inlineStr">
         <is>
           <t>条数</t>
         </is>
       </c>
-      <c r="KH1" t="inlineStr">
+      <c r="KJ1" t="inlineStr">
         <is>
           <t>户数</t>
         </is>
       </c>
-      <c r="KI1" t="inlineStr">
+      <c r="KK1" t="inlineStr">
         <is>
           <t>笔数</t>
         </is>
       </c>
-      <c r="KJ1" t="inlineStr">
+      <c r="KL1" t="inlineStr">
         <is>
           <t>车数</t>
         </is>
       </c>
-      <c r="KK1" t="inlineStr">
+      <c r="KM1" t="inlineStr">
         <is>
           <t>头数</t>
         </is>
       </c>
-      <c r="KL1" t="inlineStr">
+      <c r="KN1" t="inlineStr">
         <is>
           <t>只数</t>
         </is>
       </c>
-      <c r="KM1" t="inlineStr">
+      <c r="KO1" t="inlineStr">
         <is>
           <t>间数</t>
         </is>
       </c>
-      <c r="KN1" t="inlineStr">
+      <c r="KP1" t="inlineStr">
         <is>
           <t>亩数</t>
         </is>
       </c>
-      <c r="KO1" t="inlineStr">
+      <c r="KQ1" t="inlineStr">
         <is>
           <t>套数</t>
         </is>
       </c>
-      <c r="KP1" t="inlineStr">
+      <c r="KR1" t="inlineStr">
         <is>
           <t>项数</t>
         </is>
       </c>
-      <c r="KQ1" t="inlineStr">
+      <c r="KS1" t="inlineStr">
         <is>
           <t>总数</t>
         </is>
       </c>
-      <c r="KR1" t="inlineStr">
+      <c r="KT1" t="inlineStr">
         <is>
           <t>积分</t>
         </is>
       </c>
-      <c r="KS1" t="inlineStr">
+      <c r="KU1" t="inlineStr">
         <is>
           <t>票数</t>
         </is>
       </c>
-      <c r="KT1" t="inlineStr">
+      <c r="KV1" t="inlineStr">
         <is>
           <t>名额</t>
         </is>
       </c>
-      <c r="KU1" t="inlineStr">
+      <c r="KW1" t="inlineStr">
         <is>
           <t>席位</t>
         </is>
       </c>
-      <c r="KV1" t="inlineStr">
+      <c r="KX1" t="inlineStr">
         <is>
           <t>床位</t>
         </is>
       </c>
-      <c r="KW1" t="inlineStr">
+      <c r="KY1" t="inlineStr">
         <is>
           <t>车位</t>
         </is>
       </c>
-      <c r="KX1" t="inlineStr">
+      <c r="KZ1" t="inlineStr">
         <is>
           <t>家数</t>
         </is>
       </c>
-      <c r="KY1" t="inlineStr">
+      <c r="LA1" t="inlineStr">
         <is>
           <t>座数</t>
         </is>
       </c>
-      <c r="KZ1" t="inlineStr">
+      <c r="LB1" t="inlineStr">
         <is>
           <t>部数</t>
         </is>
       </c>
-      <c r="LA1" t="inlineStr">
+      <c r="LC1" t="inlineStr">
         <is>
           <t>册数</t>
         </is>
       </c>
-      <c r="LB1" t="inlineStr">
+      <c r="LD1" t="inlineStr">
         <is>
           <t>卷数</t>
         </is>
       </c>
-      <c r="LC1" t="inlineStr">
+      <c r="LE1" t="inlineStr">
         <is>
           <t>箱数</t>
         </is>
       </c>
-      <c r="LD1" t="inlineStr">
+      <c r="LF1" t="inlineStr">
         <is>
           <t>袋数</t>
         </is>
       </c>
-      <c r="LE1" t="inlineStr">
+      <c r="LG1" t="inlineStr">
         <is>
           <t>瓶数</t>
         </is>
       </c>
-      <c r="LF1" t="inlineStr">
+      <c r="LH1" t="inlineStr">
         <is>
           <t>轮数</t>
         </is>
       </c>
-      <c r="LG1" t="inlineStr">
+      <c r="LI1" t="inlineStr">
         <is>
           <t>批数</t>
         </is>
       </c>
-      <c r="LH1" t="inlineStr">
+      <c r="LJ1" t="inlineStr">
         <is>
           <t>课时</t>
         </is>
       </c>
-      <c r="LI1" t="inlineStr">
+      <c r="LK1" t="inlineStr">
         <is>
           <t>学分</t>
         </is>
       </c>
-      <c r="LJ1" t="inlineStr">
+      <c r="LL1" t="inlineStr">
         <is>
           <t>题数</t>
         </is>
       </c>
-      <c r="LK1" t="inlineStr">
+      <c r="LM1" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="LL1" t="inlineStr">
+      <c r="LN1" t="inlineStr">
         <is>
           <t>集数</t>
         </is>
       </c>
-      <c r="LM1" t="inlineStr">
+      <c r="LO1" t="inlineStr">
         <is>
           <t>股数</t>
         </is>
       </c>
-      <c r="LN1" t="inlineStr">
+      <c r="LP1" t="inlineStr">
         <is>
           <t>频次</t>
         </is>
       </c>
-      <c r="LO1" t="inlineStr">
+      <c r="LQ1" t="inlineStr">
         <is>
           <t>人次</t>
         </is>
       </c>
-      <c r="LP1" t="inlineStr">
+      <c r="LR1" t="inlineStr">
         <is>
           <t>班次</t>
         </is>
       </c>
-      <c r="LQ1" t="inlineStr">
+      <c r="LS1" t="inlineStr">
         <is>
           <t>车次</t>
         </is>
       </c>
-      <c r="LR1" t="inlineStr">
+      <c r="LT1" t="inlineStr">
         <is>
           <t>趟次</t>
         </is>
       </c>
-      <c r="LS1" t="inlineStr">
+      <c r="LU1" t="inlineStr">
         <is>
           <t>架次</t>
         </is>
       </c>
-      <c r="LT1" t="inlineStr">
+      <c r="LV1" t="inlineStr">
         <is>
           <t>艘次</t>
         </is>
       </c>
-      <c r="LU1" t="inlineStr">
+      <c r="LW1" t="inlineStr">
         <is>
           <t>轮次</t>
         </is>
       </c>
-      <c r="LV1" t="inlineStr">
+      <c r="LX1" t="inlineStr">
         <is>
           <t>届次</t>
         </is>
       </c>
-      <c r="LW1" t="inlineStr">
+      <c r="LY1" t="inlineStr">
         <is>
           <t>期次</t>
         </is>
       </c>
-      <c r="LX1" t="inlineStr">
+      <c r="LZ1" t="inlineStr">
         <is>
           <t>户次</t>
         </is>
       </c>
-      <c r="LY1" t="inlineStr">
+      <c r="MA1" t="inlineStr">
         <is>
           <t>根数</t>
         </is>
       </c>
-      <c r="LZ1" t="inlineStr">
+      <c r="MB1" t="inlineStr">
         <is>
           <t>块数</t>
         </is>
       </c>
-      <c r="MA1" t="inlineStr">
+      <c r="MC1" t="inlineStr">
         <is>
           <t>片数</t>
         </is>
       </c>
-      <c r="MB1" t="inlineStr">
+      <c r="MD1" t="inlineStr">
         <is>
           <t>栋数</t>
         </is>
       </c>
-      <c r="MC1" t="inlineStr">
+      <c r="ME1" t="inlineStr">
         <is>
           <t>幢数</t>
         </is>
       </c>
-      <c r="MD1" t="inlineStr">
+      <c r="MF1" t="inlineStr">
         <is>
           <t>孔数</t>
         </is>
       </c>
-      <c r="ME1" t="inlineStr">
+      <c r="MG1" t="inlineStr">
         <is>
           <t>份数</t>
         </is>
       </c>
-      <c r="MF1" t="inlineStr">
+      <c r="MH1" t="inlineStr">
         <is>
           <t>宗数</t>
         </is>
       </c>
-      <c r="MG1" t="inlineStr">
+      <c r="MI1" t="inlineStr">
         <is>
           <t>组数</t>
         </is>
       </c>
-      <c r="MH1" t="inlineStr">
+      <c r="MJ1" t="inlineStr">
         <is>
           <t>排数</t>
         </is>
       </c>
-      <c r="MI1" t="inlineStr">
+      <c r="MK1" t="inlineStr">
         <is>
           <t>行数</t>
         </is>
       </c>
-      <c r="MJ1" t="inlineStr">
+      <c r="ML1" t="inlineStr">
         <is>
           <t>列数</t>
         </is>
       </c>
-      <c r="MK1" t="inlineStr">
+      <c r="MM1" t="inlineStr">
         <is>
           <t>栏数</t>
         </is>
       </c>
-      <c r="ML1" t="inlineStr">
+      <c r="MN1" t="inlineStr">
         <is>
           <t>遍数</t>
         </is>
       </c>
-      <c r="MM1" t="inlineStr">
+      <c r="MO1" t="inlineStr">
         <is>
           <t>站点数</t>
         </is>
       </c>
-      <c r="MN1" t="inlineStr">
+      <c r="MP1" t="inlineStr">
         <is>
           <t>接口数</t>
         </is>
       </c>
-      <c r="MO1" t="inlineStr">
+      <c r="MQ1" t="inlineStr">
         <is>
           <t>端口数</t>
         </is>
       </c>
-      <c r="MP1" t="inlineStr">
+      <c r="MR1" t="inlineStr">
         <is>
           <t>会员数</t>
         </is>
       </c>
-      <c r="MQ1" t="inlineStr">
+      <c r="MS1" t="inlineStr">
         <is>
           <t>用户数</t>
         </is>
       </c>
-      <c r="MR1" t="inlineStr">
+      <c r="MT1" t="inlineStr">
         <is>
           <t>访客数</t>
         </is>
       </c>
-      <c r="MS1" t="inlineStr">
+      <c r="MU1" t="inlineStr">
         <is>
           <t>员工数</t>
         </is>
       </c>
-      <c r="MT1" t="inlineStr">
+      <c r="MV1" t="inlineStr">
         <is>
           <t>职工数</t>
         </is>
       </c>
-      <c r="MU1" t="inlineStr">
+      <c r="MW1" t="inlineStr">
         <is>
           <t>学生数</t>
         </is>
       </c>
-      <c r="MV1" t="inlineStr">
+      <c r="MX1" t="inlineStr">
         <is>
           <t>教师数</t>
         </is>
       </c>
-      <c r="MW1" t="inlineStr">
+      <c r="MY1" t="inlineStr">
         <is>
           <t>企业数</t>
         </is>
       </c>
-      <c r="MX1" t="inlineStr">
+      <c r="MZ1" t="inlineStr">
         <is>
           <t>学校数</t>
         </is>
       </c>
-      <c r="MY1" t="inlineStr">
+      <c r="NA1" t="inlineStr">
         <is>
           <t>项目数</t>
         </is>
       </c>
-      <c r="MZ1" t="inlineStr">
+      <c r="NB1" t="inlineStr">
         <is>
           <t>案件数</t>
         </is>
       </c>
-      <c r="NA1" t="inlineStr">
+      <c r="NC1" t="inlineStr">
         <is>
           <t>订单数</t>
         </is>
       </c>
-      <c r="NB1" t="inlineStr">
+      <c r="ND1" t="inlineStr">
         <is>
           <t>交易量</t>
         </is>
       </c>
-      <c r="NC1" t="inlineStr">
+      <c r="NE1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="ND1" t="inlineStr">
+      <c r="NF1" t="inlineStr">
         <is>
           <t>出货量</t>
         </is>
       </c>
-      <c r="NE1" t="inlineStr">
+      <c r="NG1" t="inlineStr">
         <is>
           <t>进货量</t>
         </is>
       </c>
-      <c r="NF1" t="inlineStr">
+      <c r="NH1" t="inlineStr">
         <is>
           <t>销售量</t>
         </is>
       </c>
-      <c r="NG1" t="inlineStr">
+      <c r="NI1" t="inlineStr">
         <is>
           <t>销量</t>
         </is>
       </c>
-      <c r="NH1" t="inlineStr">
+      <c r="NJ1" t="inlineStr">
         <is>
           <t>产量</t>
         </is>
       </c>
-      <c r="NI1" t="inlineStr">
+      <c r="NK1" t="inlineStr">
         <is>
           <t>存量</t>
         </is>
       </c>
-      <c r="NJ1" t="inlineStr">
+      <c r="NL1" t="inlineStr">
         <is>
           <t>余量</t>
         </is>
       </c>
-      <c r="NK1" t="inlineStr">
+      <c r="NM1" t="inlineStr">
         <is>
           <t>出库数</t>
         </is>
       </c>
-      <c r="NL1" t="inlineStr">
+      <c r="NN1" t="inlineStr">
         <is>
           <t>入库数</t>
         </is>
       </c>
-      <c r="NM1" t="inlineStr">
+      <c r="NO1" t="inlineStr">
         <is>
           <t>在库数</t>
         </is>
       </c>
-      <c r="NN1" t="inlineStr">
+      <c r="NP1" t="inlineStr">
         <is>
           <t>在册数</t>
         </is>
       </c>
-      <c r="NO1" t="inlineStr">
+      <c r="NQ1" t="inlineStr">
         <is>
           <t>在位数</t>
         </is>
       </c>
-      <c r="NP1" t="inlineStr">
+      <c r="NR1" t="inlineStr">
         <is>
           <t>配发数</t>
         </is>
       </c>
-      <c r="NQ1" t="inlineStr">
+      <c r="NS1" t="inlineStr">
         <is>
           <t>消耗数</t>
         </is>
       </c>
-      <c r="NR1" t="inlineStr">
+      <c r="NT1" t="inlineStr">
         <is>
           <t>报废数</t>
         </is>
       </c>
-      <c r="NS1" t="inlineStr">
+      <c r="NU1" t="inlineStr">
         <is>
           <t>维修数</t>
         </is>
       </c>
-      <c r="NT1" t="inlineStr">
+      <c r="NV1" t="inlineStr">
         <is>
           <t>检修数</t>
         </is>
       </c>
-      <c r="NU1" t="inlineStr">
+      <c r="NW1" t="inlineStr">
         <is>
           <t>领用数</t>
         </is>
       </c>
-      <c r="NV1" t="inlineStr">
+      <c r="NX1" t="inlineStr">
         <is>
           <t>归还数</t>
         </is>
       </c>
-      <c r="NW1" t="inlineStr">
+      <c r="NY1" t="inlineStr">
         <is>
           <t>发放数</t>
         </is>
       </c>
-      <c r="NX1" t="inlineStr">
+      <c r="NZ1" t="inlineStr">
         <is>
           <t>盘盈数</t>
         </is>
       </c>
-      <c r="NY1" t="inlineStr">
+      <c r="OA1" t="inlineStr">
         <is>
           <t>盘亏数</t>
         </is>
       </c>
-      <c r="NZ1" t="inlineStr">
+      <c r="OB1" t="inlineStr">
         <is>
           <t>官兵数</t>
         </is>
       </c>
-      <c r="OA1" t="inlineStr">
+      <c r="OC1" t="inlineStr">
         <is>
           <t>兵员数</t>
         </is>
       </c>
-      <c r="OB1" t="inlineStr">
+      <c r="OD1" t="inlineStr">
         <is>
           <t>装备数</t>
         </is>
       </c>
-      <c r="OC1" t="inlineStr">
+      <c r="OE1" t="inlineStr">
         <is>
           <t>台套数</t>
         </is>
       </c>
-      <c r="OD1" t="inlineStr">
+      <c r="OF1" t="inlineStr">
         <is>
           <t>辆数</t>
         </is>
       </c>
-      <c r="OE1" t="inlineStr">
+      <c r="OG1" t="inlineStr">
         <is>
           <t>参与数</t>
         </is>
       </c>
-      <c r="OF1" t="inlineStr">
+      <c r="OH1" t="inlineStr">
+        <is>
+          <t>心率</t>
+        </is>
+      </c>
+      <c r="OI1" t="inlineStr">
+        <is>
+          <t>脉搏</t>
+        </is>
+      </c>
+      <c r="OJ1" t="inlineStr">
+        <is>
+          <t>剂次</t>
+        </is>
+      </c>
+      <c r="OK1" t="inlineStr">
+        <is>
+          <t>环数</t>
+        </is>
+      </c>
+      <c r="OL1" t="inlineStr">
+        <is>
+          <t>圈数</t>
+        </is>
+      </c>
+      <c r="OM1" t="inlineStr">
         <is>
           <t>长度</t>
         </is>
       </c>
-      <c r="OG1" t="inlineStr">
+      <c r="ON1" t="inlineStr">
         <is>
           <t>宽度</t>
         </is>
       </c>
-      <c r="OH1" t="inlineStr">
+      <c r="OO1" t="inlineStr">
         <is>
           <t>高度</t>
         </is>
       </c>
-      <c r="OI1" t="inlineStr">
+      <c r="OP1" t="inlineStr">
         <is>
           <t>厚度</t>
         </is>
       </c>
-      <c r="OJ1" t="inlineStr">
+      <c r="OQ1" t="inlineStr">
         <is>
           <t>深度</t>
         </is>
       </c>
-      <c r="OK1" t="inlineStr">
+      <c r="OR1" t="inlineStr">
         <is>
           <t>距离</t>
         </is>
       </c>
-      <c r="OL1" t="inlineStr">
+      <c r="OS1" t="inlineStr">
         <is>
           <t>里程</t>
         </is>
       </c>
-      <c r="OM1" t="inlineStr">
+      <c r="OT1" t="inlineStr">
         <is>
           <t>面积</t>
         </is>
       </c>
-      <c r="ON1" t="inlineStr">
+      <c r="OU1" t="inlineStr">
         <is>
           <t>体积</t>
         </is>
       </c>
-      <c r="OO1" t="inlineStr">
+      <c r="OV1" t="inlineStr">
         <is>
           <t>容积</t>
         </is>
       </c>
-      <c r="OP1" t="inlineStr">
+      <c r="OW1" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="OQ1" t="inlineStr">
+      <c r="OX1" t="inlineStr">
         <is>
           <t>毛重</t>
         </is>
       </c>
-      <c r="OR1" t="inlineStr">
+      <c r="OY1" t="inlineStr">
         <is>
           <t>净重</t>
         </is>
       </c>
-      <c r="OS1" t="inlineStr">
+      <c r="OZ1" t="inlineStr">
         <is>
           <t>体重</t>
         </is>
       </c>
-      <c r="OT1" t="inlineStr">
+      <c r="PA1" t="inlineStr">
         <is>
           <t>载重</t>
         </is>
       </c>
-      <c r="OU1" t="inlineStr">
+      <c r="PB1" t="inlineStr">
         <is>
           <t>容量</t>
         </is>
       </c>
-      <c r="OV1" t="inlineStr">
+      <c r="PC1" t="inlineStr">
         <is>
           <t>温度</t>
         </is>
       </c>
-      <c r="OW1" t="inlineStr">
+      <c r="PD1" t="inlineStr">
         <is>
           <t>湿度</t>
         </is>
       </c>
-      <c r="OX1" t="inlineStr">
+      <c r="PE1" t="inlineStr">
         <is>
           <t>浓度</t>
         </is>
       </c>
-      <c r="OY1" t="inlineStr">
+      <c r="PF1" t="inlineStr">
         <is>
           <t>密度</t>
         </is>
       </c>
-      <c r="OZ1" t="inlineStr">
+      <c r="PG1" t="inlineStr">
         <is>
           <t>压力</t>
         </is>
       </c>
-      <c r="PA1" t="inlineStr">
+      <c r="PH1" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
-      <c r="PB1" t="inlineStr">
+      <c r="PI1" t="inlineStr">
         <is>
           <t>速率</t>
         </is>
       </c>
-      <c r="PC1" t="inlineStr">
+      <c r="PJ1" t="inlineStr">
         <is>
           <t>流量</t>
         </is>
       </c>
-      <c r="PD1" t="inlineStr">
+      <c r="PK1" t="inlineStr">
         <is>
           <t>电量</t>
         </is>
       </c>
-      <c r="PE1" t="inlineStr">
+      <c r="PL1" t="inlineStr">
         <is>
           <t>水量</t>
         </is>
       </c>
-      <c r="PF1" t="inlineStr">
+      <c r="PM1" t="inlineStr">
         <is>
           <t>气量</t>
         </is>
       </c>
-      <c r="PG1" t="inlineStr">
+      <c r="PN1" t="inlineStr">
         <is>
           <t>热量</t>
         </is>
       </c>
-      <c r="PH1" t="inlineStr">
+      <c r="PO1" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
-      <c r="PI1" t="inlineStr">
+      <c r="PP1" t="inlineStr">
         <is>
           <t>电压</t>
         </is>
       </c>
-      <c r="PJ1" t="inlineStr">
+      <c r="PQ1" t="inlineStr">
         <is>
           <t>电流</t>
         </is>
       </c>
-      <c r="PK1" t="inlineStr">
+      <c r="PR1" t="inlineStr">
         <is>
           <t>频率</t>
         </is>
       </c>
-      <c r="PL1" t="inlineStr">
+      <c r="PS1" t="inlineStr">
         <is>
           <t>海拔</t>
         </is>
       </c>
-      <c r="PM1" t="inlineStr">
+      <c r="PT1" t="inlineStr">
         <is>
           <t>高程</t>
         </is>
       </c>
-      <c r="PN1" t="inlineStr">
+      <c r="PU1" t="inlineStr">
         <is>
           <t>水位</t>
         </is>
       </c>
-      <c r="PO1" t="inlineStr">
+      <c r="PV1" t="inlineStr">
         <is>
           <t>雨量</t>
         </is>
       </c>
-      <c r="PP1" t="inlineStr">
+      <c r="PW1" t="inlineStr">
         <is>
           <t>身高</t>
         </is>
       </c>
-      <c r="PQ1" t="inlineStr">
+      <c r="PX1" t="inlineStr">
         <is>
           <t>含量</t>
         </is>
       </c>
-      <c r="PR1" t="inlineStr">
+      <c r="PY1" t="inlineStr">
         <is>
           <t>纯度</t>
         </is>
       </c>
-      <c r="PS1" t="inlineStr">
+      <c r="PZ1" t="inlineStr">
         <is>
           <t>直径</t>
         </is>
       </c>
-      <c r="PT1" t="inlineStr">
+      <c r="QA1" t="inlineStr">
         <is>
           <t>半径</t>
         </is>
       </c>
-      <c r="PU1" t="inlineStr">
+      <c r="QB1" t="inlineStr">
         <is>
           <t>周长</t>
         </is>
       </c>
-      <c r="PV1" t="inlineStr">
+      <c r="QC1" t="inlineStr">
         <is>
           <t>角度</t>
         </is>
       </c>
-      <c r="PW1" t="inlineStr">
+      <c r="QD1" t="inlineStr">
         <is>
           <t>间距</t>
         </is>
       </c>
-      <c r="PX1" t="inlineStr">
+      <c r="QE1" t="inlineStr">
         <is>
           <t>跨度</t>
         </is>
       </c>
-      <c r="PY1" t="inlineStr">
+      <c r="QF1" t="inlineStr">
         <is>
           <t>坡度</t>
         </is>
       </c>
-      <c r="PZ1" t="inlineStr">
+      <c r="QG1" t="inlineStr">
         <is>
           <t>倾斜度</t>
         </is>
       </c>
-      <c r="QA1" t="inlineStr">
+      <c r="QH1" t="inlineStr">
         <is>
           <t>粗糙度</t>
         </is>
       </c>
-      <c r="QB1" t="inlineStr">
+      <c r="QI1" t="inlineStr">
         <is>
           <t>平整度</t>
         </is>
       </c>
-      <c r="QC1" t="inlineStr">
+      <c r="QJ1" t="inlineStr">
         <is>
           <t>压实度</t>
         </is>
       </c>
-      <c r="QD1" t="inlineStr">
+      <c r="QK1" t="inlineStr">
         <is>
           <t>稠度</t>
         </is>
       </c>
-      <c r="QE1" t="inlineStr">
+      <c r="QL1" t="inlineStr">
         <is>
           <t>黏度</t>
         </is>
       </c>
-      <c r="QF1" t="inlineStr">
+      <c r="QM1" t="inlineStr">
         <is>
           <t>粘度</t>
         </is>
       </c>
-      <c r="QG1" t="inlineStr">
+      <c r="QN1" t="inlineStr">
         <is>
           <t>硬度</t>
         </is>
       </c>
-      <c r="QH1" t="inlineStr">
+      <c r="QO1" t="inlineStr">
         <is>
           <t>强度</t>
         </is>
       </c>
-      <c r="QI1" t="inlineStr">
+      <c r="QP1" t="inlineStr">
         <is>
           <t>应力</t>
         </is>
       </c>
-      <c r="QJ1" t="inlineStr">
+      <c r="QQ1" t="inlineStr">
         <is>
           <t>应变</t>
         </is>
       </c>
-      <c r="QK1" t="inlineStr">
+      <c r="QR1" t="inlineStr">
         <is>
           <t>模量</t>
         </is>
       </c>
-      <c r="QL1" t="inlineStr">
+      <c r="QS1" t="inlineStr">
         <is>
           <t>电阻</t>
         </is>
       </c>
-      <c r="QM1" t="inlineStr">
+      <c r="QT1" t="inlineStr">
         <is>
           <t>电容</t>
         </is>
       </c>
-      <c r="QN1" t="inlineStr">
+      <c r="QU1" t="inlineStr">
         <is>
           <t>电感</t>
         </is>
       </c>
-      <c r="QO1" t="inlineStr">
+      <c r="QV1" t="inlineStr">
         <is>
           <t>阻抗</t>
         </is>
       </c>
-      <c r="QP1" t="inlineStr">
+      <c r="QW1" t="inlineStr">
         <is>
           <t>能耗</t>
         </is>
       </c>
-      <c r="QQ1" t="inlineStr">
+      <c r="QX1" t="inlineStr">
         <is>
           <t>电耗</t>
         </is>
       </c>
-      <c r="QR1" t="inlineStr">
+      <c r="QY1" t="inlineStr">
         <is>
           <t>水耗</t>
         </is>
       </c>
-      <c r="QS1" t="inlineStr">
+      <c r="QZ1" t="inlineStr">
         <is>
           <t>热耗</t>
         </is>
       </c>
-      <c r="QT1" t="inlineStr">
+      <c r="RA1" t="inlineStr">
         <is>
           <t>油耗</t>
         </is>
       </c>
-      <c r="QU1" t="inlineStr">
+      <c r="RB1" t="inlineStr">
         <is>
           <t>气耗</t>
         </is>
       </c>
-      <c r="QV1" t="inlineStr">
+      <c r="RC1" t="inlineStr">
         <is>
           <t>煤耗</t>
         </is>
       </c>
-      <c r="QW1" t="inlineStr">
+      <c r="RD1" t="inlineStr">
         <is>
           <t>产能</t>
         </is>
       </c>
-      <c r="QX1" t="inlineStr">
+      <c r="RE1" t="inlineStr">
         <is>
           <t>吨位</t>
         </is>
       </c>
-      <c r="QY1" t="inlineStr">
+      <c r="RF1" t="inlineStr">
         <is>
           <t>载荷</t>
         </is>
       </c>
-      <c r="QZ1" t="inlineStr">
+      <c r="RG1" t="inlineStr">
         <is>
           <t>荷载</t>
         </is>
       </c>
-      <c r="RA1" t="inlineStr">
+      <c r="RH1" t="inlineStr">
         <is>
           <t>压强</t>
         </is>
       </c>
-      <c r="RB1" t="inlineStr">
+      <c r="RI1" t="inlineStr">
         <is>
           <t>液压</t>
         </is>
       </c>
-      <c r="RC1" t="inlineStr">
+      <c r="RJ1" t="inlineStr">
         <is>
           <t>气压</t>
         </is>
       </c>
-      <c r="RD1" t="inlineStr">
+      <c r="RK1" t="inlineStr">
         <is>
           <t>风速</t>
         </is>
       </c>
-      <c r="RE1" t="inlineStr">
+      <c r="RL1" t="inlineStr">
         <is>
           <t>流速</t>
         </is>
       </c>
-      <c r="RF1" t="inlineStr">
+      <c r="RM1" t="inlineStr">
         <is>
           <t>照度</t>
         </is>
       </c>
-      <c r="RG1" t="inlineStr">
+      <c r="RN1" t="inlineStr">
         <is>
           <t>亮度</t>
         </is>
       </c>
-      <c r="RH1" t="inlineStr">
+      <c r="RO1" t="inlineStr">
         <is>
           <t>色度</t>
         </is>
       </c>
-      <c r="RI1" t="inlineStr">
+      <c r="RP1" t="inlineStr">
         <is>
           <t>浊度</t>
         </is>
       </c>
-      <c r="RJ1" t="inlineStr">
+      <c r="RQ1" t="inlineStr">
         <is>
           <t>盐度</t>
         </is>
       </c>
-      <c r="RK1" t="inlineStr">
+      <c r="RR1" t="inlineStr">
         <is>
           <t>酸度</t>
         </is>
       </c>
-      <c r="RL1" t="inlineStr">
+      <c r="RS1" t="inlineStr">
         <is>
           <t>碱度</t>
         </is>
       </c>
-      <c r="RM1" t="inlineStr">
+      <c r="RT1" t="inlineStr">
         <is>
           <t>温差</t>
         </is>
       </c>
-      <c r="RN1" t="inlineStr">
+      <c r="RU1" t="inlineStr">
         <is>
           <t>体温</t>
         </is>
       </c>
-      <c r="RO1" t="inlineStr">
+      <c r="RV1" t="inlineStr">
         <is>
           <t>扬程</t>
         </is>
       </c>
-      <c r="RP1" t="inlineStr">
+      <c r="RW1" t="inlineStr">
         <is>
           <t>库容</t>
         </is>
       </c>
-      <c r="RQ1" t="inlineStr">
+      <c r="RX1" t="inlineStr">
         <is>
           <t>含沙量</t>
         </is>
       </c>
-      <c r="RR1" t="inlineStr">
+      <c r="RY1" t="inlineStr">
         <is>
           <t>溶解氧</t>
         </is>
       </c>
-      <c r="RS1" t="inlineStr">
+      <c r="RZ1" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="RT1" t="inlineStr">
+      <c r="SA1" t="inlineStr">
         <is>
           <t>断面</t>
         </is>
       </c>
-      <c r="RU1" t="inlineStr">
+      <c r="SB1" t="inlineStr">
         <is>
           <t>管径</t>
         </is>
       </c>
-      <c r="RV1" t="inlineStr">
+      <c r="SC1" t="inlineStr">
         <is>
           <t>线径</t>
         </is>
       </c>
-      <c r="RW1" t="inlineStr">
+      <c r="SD1" t="inlineStr">
         <is>
           <t>粒径</t>
         </is>
       </c>
-      <c r="RX1" t="inlineStr">
+      <c r="SE1" t="inlineStr">
         <is>
           <t>粒度</t>
         </is>
       </c>
-      <c r="RY1" t="inlineStr">
+      <c r="SF1" t="inlineStr">
         <is>
           <t>负荷</t>
         </is>
       </c>
-      <c r="RZ1" t="inlineStr">
+      <c r="SG1" t="inlineStr">
         <is>
           <t>壁厚</t>
         </is>
       </c>
-      <c r="SA1" t="inlineStr">
+      <c r="SH1" t="inlineStr">
         <is>
           <t>净高</t>
         </is>
       </c>
-      <c r="SB1" t="inlineStr">
+      <c r="SI1" t="inlineStr">
         <is>
           <t>净空</t>
         </is>
       </c>
-      <c r="SC1" t="inlineStr">
+      <c r="SJ1" t="inlineStr">
         <is>
           <t>埋深</t>
         </is>
       </c>
-      <c r="SD1" t="inlineStr">
+      <c r="SK1" t="inlineStr">
         <is>
           <t>覆土</t>
         </is>
       </c>
-      <c r="SE1" t="inlineStr">
+      <c r="SL1" t="inlineStr">
         <is>
           <t>进深</t>
         </is>
       </c>
-      <c r="SF1" t="inlineStr">
+      <c r="SM1" t="inlineStr">
         <is>
           <t>开间</t>
         </is>
       </c>
-      <c r="SG1" t="inlineStr">
+      <c r="SN1" t="inlineStr">
         <is>
           <t>视距</t>
         </is>
       </c>
-      <c r="SH1" t="inlineStr">
+      <c r="SO1" t="inlineStr">
         <is>
           <t>弧长</t>
         </is>
       </c>
-      <c r="SI1" t="inlineStr">
+      <c r="SP1" t="inlineStr">
         <is>
           <t>弦长</t>
         </is>
       </c>
-      <c r="SJ1" t="inlineStr">
+      <c r="SQ1" t="inlineStr">
         <is>
           <t>振幅</t>
         </is>
       </c>
-      <c r="SK1" t="inlineStr">
+      <c r="SR1" t="inlineStr">
         <is>
           <t>挠度</t>
         </is>
       </c>
-      <c r="SL1" t="inlineStr">
+      <c r="SS1" t="inlineStr">
         <is>
           <t>沉降</t>
         </is>
       </c>
-      <c r="SM1" t="inlineStr">
+      <c r="ST1" t="inlineStr">
         <is>
           <t>位移</t>
         </is>
       </c>
-      <c r="SN1" t="inlineStr">
+      <c r="SU1" t="inlineStr">
         <is>
           <t>变形量</t>
         </is>
       </c>
-      <c r="SO1" t="inlineStr">
+      <c r="SV1" t="inlineStr">
         <is>
           <t>噪声</t>
         </is>
       </c>
-      <c r="SP1" t="inlineStr">
+      <c r="SW1" t="inlineStr">
         <is>
           <t>噪音</t>
         </is>
       </c>
-      <c r="SQ1" t="inlineStr">
+      <c r="SX1" t="inlineStr">
         <is>
           <t>分贝</t>
         </is>
       </c>
-      <c r="SR1" t="inlineStr">
+      <c r="SY1" t="inlineStr">
         <is>
           <t>辐射</t>
         </is>
       </c>
-      <c r="SS1" t="inlineStr">
+      <c r="SZ1" t="inlineStr">
         <is>
           <t>总磷</t>
         </is>
       </c>
-      <c r="ST1" t="inlineStr">
+      <c r="TA1" t="inlineStr">
         <is>
           <t>总氮</t>
         </is>
       </c>
-      <c r="SU1" t="inlineStr">
+      <c r="TB1" t="inlineStr">
         <is>
           <t>含水</t>
         </is>
       </c>
-      <c r="SV1" t="inlineStr">
+      <c r="TC1" t="inlineStr">
         <is>
           <t>航程</t>
         </is>
       </c>
-      <c r="SW1" t="inlineStr">
+      <c r="TD1" t="inlineStr">
         <is>
           <t>航速</t>
         </is>
       </c>
-      <c r="SX1" t="inlineStr">
+      <c r="TE1" t="inlineStr">
         <is>
           <t>转速</t>
         </is>
       </c>
-      <c r="SY1" t="inlineStr">
+      <c r="TF1" t="inlineStr">
         <is>
           <t>亩产</t>
         </is>
       </c>
-      <c r="SZ1" t="inlineStr">
+      <c r="TG1" t="inlineStr">
+        <is>
+          <t>血糖</t>
+        </is>
+      </c>
+      <c r="TH1" t="inlineStr">
+        <is>
+          <t>视力</t>
+        </is>
+      </c>
+      <c r="TI1" t="inlineStr">
+        <is>
+          <t>剂量</t>
+        </is>
+      </c>
+      <c r="TJ1" t="inlineStr">
+        <is>
+          <t>用药量</t>
+        </is>
+      </c>
+      <c r="TK1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="TA1" t="inlineStr">
+      <c r="TL1" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="TB1" t="inlineStr">
+      <c r="TM1" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="TC1" t="inlineStr">
+      <c r="TN1" t="inlineStr">
         <is>
           <t>名次</t>
         </is>
       </c>
-      <c r="TD1" t="inlineStr">
+      <c r="TO1" t="inlineStr">
         <is>
           <t>页码</t>
         </is>
       </c>
-      <c r="TE1" t="inlineStr">
+      <c r="TP1" t="inlineStr">
         <is>
           <t>页数</t>
         </is>
       </c>
-      <c r="TF1" t="inlineStr">
+      <c r="TQ1" t="inlineStr">
         <is>
           <t>层数</t>
         </is>
       </c>
-      <c r="TG1" t="inlineStr">
+      <c r="TR1" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="TH1" t="inlineStr">
+      <c r="TS1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="TI1" t="inlineStr">
+      <c r="TT1" t="inlineStr">
         <is>
           <t>位次</t>
         </is>
       </c>
-      <c r="TJ1" t="inlineStr">
+      <c r="TU1" t="inlineStr">
         <is>
           <t>座次</t>
         </is>
       </c>
-      <c r="TK1" t="inlineStr">
+      <c r="TV1" t="inlineStr">
         <is>
           <t>位序</t>
         </is>
       </c>
-      <c r="TL1" t="inlineStr">
+      <c r="TW1" t="inlineStr">
         <is>
           <t>顺位</t>
         </is>
       </c>
-      <c r="TM1" t="inlineStr">
+      <c r="TX1" t="inlineStr">
         <is>
           <t>序位</t>
         </is>
       </c>
-      <c r="TN1" t="inlineStr">
+      <c r="TY1" t="inlineStr">
         <is>
           <t>比例</t>
         </is>
       </c>
-      <c r="TO1" t="inlineStr">
+      <c r="TZ1" t="inlineStr">
         <is>
           <t>百分比</t>
         </is>
       </c>
-      <c r="TP1" t="inlineStr">
+      <c r="UA1" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
-      <c r="TQ1" t="inlineStr">
+      <c r="UB1" t="inlineStr">
         <is>
           <t>增速</t>
         </is>
       </c>
-      <c r="TR1" t="inlineStr">
+      <c r="UC1" t="inlineStr">
         <is>
           <t>幅度</t>
         </is>
       </c>
-      <c r="TS1" t="inlineStr">
+      <c r="UD1" t="inlineStr">
         <is>
           <t>系数</t>
         </is>
       </c>
-      <c r="TT1" t="inlineStr">
+      <c r="UE1" t="inlineStr">
         <is>
           <t>因数</t>
         </is>
       </c>
-      <c r="TU1" t="inlineStr">
+      <c r="UF1" t="inlineStr">
         <is>
           <t>倍数</t>
         </is>
       </c>
-      <c r="TV1" t="inlineStr">
+      <c r="UG1" t="inlineStr">
         <is>
           <t>折扣</t>
         </is>
       </c>
-      <c r="TW1" t="inlineStr">
+      <c r="UH1" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="TX1" t="inlineStr">
+      <c r="UI1" t="inlineStr">
         <is>
           <t>比重</t>
         </is>
       </c>
-      <c r="TY1" t="inlineStr">
+      <c r="UJ1" t="inlineStr">
         <is>
           <t>容积率</t>
         </is>
       </c>
-      <c r="TZ1" t="inlineStr">
+      <c r="UK1" t="inlineStr">
         <is>
           <t>概率</t>
         </is>
       </c>
-      <c r="UA1" t="inlineStr">
+      <c r="UL1" t="inlineStr">
         <is>
           <t>比值</t>
         </is>
       </c>
-      <c r="UB1" t="inlineStr">
+      <c r="UM1" t="inlineStr">
         <is>
           <t>份额</t>
         </is>
       </c>
-      <c r="UC1" t="inlineStr">
+      <c r="UN1" t="inlineStr">
         <is>
           <t>百分点</t>
         </is>
       </c>
-      <c r="UD1" t="inlineStr">
+      <c r="UO1" t="inlineStr">
         <is>
           <t>配比</t>
         </is>
       </c>
-      <c r="UE1" t="inlineStr">
+      <c r="UP1" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
       </c>
-      <c r="UF1" t="inlineStr">
+      <c r="UQ1" t="inlineStr">
         <is>
           <t>评分</t>
         </is>
       </c>
-      <c r="UG1" t="inlineStr">
+      <c r="UR1" t="inlineStr">
         <is>
           <t>分数</t>
         </is>
       </c>
-      <c r="UH1" t="inlineStr">
+      <c r="US1" t="inlineStr">
         <is>
           <t>成绩</t>
         </is>
       </c>
-      <c r="UI1" t="inlineStr">
+      <c r="UT1" t="inlineStr">
         <is>
           <t>总分</t>
         </is>
       </c>
-      <c r="UJ1" t="inlineStr">
+      <c r="UU1" t="inlineStr">
         <is>
           <t>平均分</t>
         </is>
       </c>
-      <c r="UK1" t="inlineStr">
+      <c r="UV1" t="inlineStr">
         <is>
           <t>绩点</t>
         </is>
       </c>
-      <c r="UL1" t="inlineStr">
+      <c r="UW1" t="inlineStr">
         <is>
           <t>分值</t>
         </is>
       </c>
-      <c r="UM1" t="inlineStr">
+      <c r="UX1" t="inlineStr">
         <is>
           <t>满意度</t>
         </is>
       </c>
-      <c r="UN1" t="inlineStr">
+      <c r="UY1" t="inlineStr">
         <is>
           <t>星级</t>
         </is>
       </c>
-      <c r="UO1" t="inlineStr">
+      <c r="UZ1" t="inlineStr">
         <is>
           <t>扣分</t>
         </is>
       </c>
-      <c r="UP1" t="inlineStr">
+      <c r="VA1" t="inlineStr">
         <is>
           <t>加分</t>
         </is>
       </c>
-      <c r="UQ1" t="inlineStr">
+      <c r="VB1" t="inlineStr">
         <is>
           <t>基准分</t>
         </is>
       </c>
-      <c r="UR1" t="inlineStr">
+      <c r="VC1" t="inlineStr">
         <is>
           <t>考核分</t>
         </is>
       </c>
-      <c r="US1" t="inlineStr">
+      <c r="VD1" t="inlineStr">
         <is>
           <t>理论分</t>
         </is>
       </c>
-      <c r="UT1" t="inlineStr">
+      <c r="VE1" t="inlineStr">
         <is>
           <t>实操分</t>
         </is>
       </c>
-      <c r="UU1" t="inlineStr">
+      <c r="VF1" t="inlineStr">
         <is>
           <t>体能分</t>
         </is>
       </c>
-      <c r="UV1" t="inlineStr">
+      <c r="VG1" t="inlineStr">
         <is>
           <t>技能分</t>
         </is>
       </c>
-      <c r="UW1" t="inlineStr">
+      <c r="VH1" t="inlineStr">
         <is>
           <t>综合分</t>
         </is>
       </c>
-      <c r="UX1" t="inlineStr">
+      <c r="VI1" t="inlineStr">
         <is>
           <t>总评</t>
         </is>
       </c>
-      <c r="UY1" t="inlineStr">
+      <c r="VJ1" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="UZ1" t="inlineStr">
+      <c r="VK1" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="VA1" t="inlineStr">
+      <c r="VL1" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="VB1" t="inlineStr">
+      <c r="VM1" t="inlineStr">
         <is>
           <t>共计</t>
         </is>
       </c>
-      <c r="VC1" t="inlineStr">
+      <c r="VN1" t="inlineStr">
         <is>
           <t>累计</t>
         </is>
       </c>
-      <c r="VD1" t="inlineStr">
+      <c r="VO1" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="VE1" t="inlineStr">
+      <c r="VP1" t="inlineStr">
         <is>
           <t>总量</t>
         </is>
       </c>
-      <c r="VF1" t="inlineStr">
+      <c r="VQ1" t="inlineStr">
         <is>
           <t>总值</t>
         </is>
       </c>
-      <c r="VG1" t="inlineStr">
+      <c r="VR1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="VH1" t="inlineStr">
+      <c r="VS1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="VI1" t="inlineStr">
+      <c r="VT1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="VJ1" t="inlineStr">
+      <c r="VU1" t="inlineStr">
         <is>
           <t>详情</t>
         </is>
       </c>
-      <c r="VK1" t="inlineStr">
+      <c r="VV1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="VL1" t="inlineStr">
+      <c r="VW1" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="VM1" t="inlineStr">
+      <c r="VX1" t="inlineStr">
         <is>
           <t>简介</t>
         </is>
       </c>
-      <c r="VN1" t="inlineStr">
+      <c r="VY1" t="inlineStr">
         <is>
           <t>评价</t>
         </is>
       </c>
-      <c r="VO1" t="inlineStr">
+      <c r="VZ1" t="inlineStr">
         <is>
           <t>意见</t>
         </is>
       </c>
-      <c r="VP1" t="inlineStr">
+      <c r="WA1" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="VQ1" t="inlineStr">
+      <c r="WB1" t="inlineStr">
         <is>
           <t>要求</t>
         </is>
       </c>
-      <c r="VR1" t="inlineStr">
+      <c r="WC1" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
       </c>
-      <c r="VS1" t="inlineStr">
+      <c r="WD1" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="VT1" t="inlineStr">
+      <c r="WE1" t="inlineStr">
         <is>
           <t>经过</t>
         </is>
       </c>
-      <c r="VU1" t="inlineStr">
+      <c r="WF1" t="inlineStr">
         <is>
           <t>措施</t>
         </is>
       </c>
-      <c r="VV1" t="inlineStr">
+      <c r="WG1" t="inlineStr">
         <is>
           <t>职责</t>
         </is>
       </c>
-      <c r="VW1" t="inlineStr">
+      <c r="WH1" t="inlineStr">
         <is>
           <t>业绩</t>
         </is>
       </c>
-      <c r="VX1" t="inlineStr">
+      <c r="WI1" t="inlineStr">
         <is>
           <t>事迹</t>
         </is>
       </c>
-      <c r="VY1" t="inlineStr">
+      <c r="WJ1" t="inlineStr">
         <is>
           <t>案情</t>
         </is>
       </c>
-      <c r="VZ1" t="inlineStr">
+      <c r="WK1" t="inlineStr">
         <is>
           <t>附注</t>
         </is>
       </c>
-      <c r="WA1" t="inlineStr">
+      <c r="WL1" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="WB1" t="inlineStr">
+      <c r="WM1" t="inlineStr">
         <is>
           <t>正文</t>
         </is>
       </c>
-      <c r="WC1" t="inlineStr">
+      <c r="WN1" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="WD1" t="inlineStr">
+      <c r="WO1" t="inlineStr">
         <is>
           <t>结论</t>
         </is>
       </c>
-      <c r="WE1" t="inlineStr">
+      <c r="WP1" t="inlineStr">
         <is>
           <t>经营范围</t>
         </is>
       </c>
-      <c r="WF1" t="inlineStr">
+      <c r="WQ1" t="inlineStr">
         <is>
           <t>注意事项</t>
         </is>
       </c>
-      <c r="WG1" t="inlineStr">
+      <c r="WR1" t="inlineStr">
         <is>
           <t>特点</t>
         </is>
       </c>
-      <c r="WH1" t="inlineStr">
+      <c r="WS1" t="inlineStr">
         <is>
           <t>优势</t>
         </is>
       </c>
-      <c r="WI1" t="inlineStr">
+      <c r="WT1" t="inlineStr">
         <is>
           <t>亮点</t>
         </is>
       </c>
-      <c r="WJ1" t="inlineStr">
+      <c r="WU1" t="inlineStr">
         <is>
           <t>留言</t>
         </is>
       </c>
-      <c r="WK1" t="inlineStr">
+      <c r="WV1" t="inlineStr">
         <is>
           <t>反馈</t>
         </is>
       </c>
-      <c r="WL1" t="inlineStr">
+      <c r="WW1" t="inlineStr">
         <is>
           <t>答复</t>
         </is>
       </c>
-      <c r="WM1" t="inlineStr">
+      <c r="WX1" t="inlineStr">
         <is>
           <t>回复</t>
         </is>
       </c>
-      <c r="WN1" t="inlineStr">
+      <c r="WY1" t="inlineStr">
         <is>
           <t>心得</t>
         </is>
       </c>
-      <c r="WO1" t="inlineStr">
+      <c r="WZ1" t="inlineStr">
         <is>
           <t>体会</t>
         </is>
       </c>
-      <c r="WP1" t="inlineStr">
+      <c r="XA1" t="inlineStr">
         <is>
           <t>感想</t>
         </is>
       </c>
-      <c r="WQ1" t="inlineStr">
+      <c r="XB1" t="inlineStr">
         <is>
           <t>承诺</t>
         </is>
       </c>
-      <c r="WR1" t="inlineStr">
+      <c r="XC1" t="inlineStr">
         <is>
           <t>条款</t>
         </is>
       </c>
-      <c r="WS1" t="inlineStr">
+      <c r="XD1" t="inlineStr">
         <is>
           <t>批注</t>
         </is>
       </c>
-      <c r="WT1" t="inlineStr">
+      <c r="XE1" t="inlineStr">
         <is>
           <t>点评</t>
         </is>
       </c>
-      <c r="WU1" t="inlineStr">
+      <c r="XF1" t="inlineStr">
         <is>
           <t>陈述</t>
         </is>
       </c>
-      <c r="WV1" t="inlineStr">
+      <c r="XG1" t="inlineStr">
         <is>
           <t>供述</t>
         </is>
       </c>
-      <c r="WW1" t="inlineStr">
+      <c r="XH1" t="inlineStr">
         <is>
           <t>证言</t>
         </is>
       </c>
-      <c r="WX1" t="inlineStr">
+      <c r="XI1" t="inlineStr">
         <is>
           <t>笔录</t>
         </is>
       </c>
-      <c r="WY1" t="inlineStr">
+      <c r="XJ1" t="inlineStr">
         <is>
           <t>诉求</t>
         </is>
       </c>
-      <c r="WZ1" t="inlineStr">
+      <c r="XK1" t="inlineStr">
         <is>
           <t>主张</t>
         </is>
       </c>
-      <c r="XA1" t="inlineStr">
+      <c r="XL1" t="inlineStr">
         <is>
           <t>情况</t>
         </is>
       </c>
-      <c r="XB1" t="inlineStr">
+      <c r="XM1" t="inlineStr">
         <is>
           <t>事由</t>
         </is>
       </c>
-      <c r="XC1" t="inlineStr">
+      <c r="XN1" t="inlineStr">
         <is>
           <t>纪要</t>
         </is>
       </c>
-      <c r="XD1" t="inlineStr">
+      <c r="XO1" t="inlineStr">
         <is>
           <t>做法</t>
         </is>
       </c>
-      <c r="XE1" t="inlineStr">
+      <c r="XP1" t="inlineStr">
         <is>
           <t>成效</t>
         </is>
       </c>
-      <c r="XF1" t="inlineStr">
+      <c r="XQ1" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="XG1" t="inlineStr">
+      <c r="XR1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="XH1" t="inlineStr">
+      <c r="XS1" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="XI1" t="inlineStr">
+      <c r="XT1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="XJ1" t="inlineStr">
+      <c r="XU1" t="inlineStr">
         <is>
           <t>题目</t>
         </is>
       </c>
-      <c r="XK1" t="inlineStr">
+      <c r="XV1" t="inlineStr">
         <is>
           <t>主题</t>
         </is>
       </c>
-      <c r="XL1" t="inlineStr">
+      <c r="XW1" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="XM1" t="inlineStr">
+      <c r="XX1" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="XN1" t="inlineStr">
+      <c r="XY1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="XO1" t="inlineStr">
+      <c r="XZ1" t="inlineStr">
         <is>
           <t>种类</t>
         </is>
       </c>
-      <c r="XP1" t="inlineStr">
+      <c r="YA1" t="inlineStr">
         <is>
           <t>品种</t>
         </is>
       </c>
-      <c r="XQ1" t="inlineStr">
+      <c r="YB1" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="XR1" t="inlineStr">
+      <c r="YC1" t="inlineStr">
         <is>
           <t>型号</t>
         </is>
       </c>
-      <c r="XS1" t="inlineStr">
+      <c r="YD1" t="inlineStr">
         <is>
           <t>规格</t>
         </is>
       </c>
-      <c r="XT1" t="inlineStr">
+      <c r="YE1" t="inlineStr">
         <is>
           <t>材质</t>
         </is>
       </c>
-      <c r="XU1" t="inlineStr">
+      <c r="YF1" t="inlineStr">
         <is>
           <t>颜色</t>
         </is>
       </c>
-      <c r="XV1" t="inlineStr">
+      <c r="YG1" t="inlineStr">
         <is>
           <t>尺码</t>
         </is>
       </c>
-      <c r="XW1" t="inlineStr">
+      <c r="YH1" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="XX1" t="inlineStr">
+      <c r="YI1" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="XY1" t="inlineStr">
+      <c r="YJ1" t="inlineStr">
         <is>
           <t>机构</t>
         </is>
       </c>
-      <c r="XZ1" t="inlineStr">
+      <c r="YK1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="YA1" t="inlineStr">
+      <c r="YL1" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="YB1" t="inlineStr">
+      <c r="YM1" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="YC1" t="inlineStr">
+      <c r="YN1" t="inlineStr">
         <is>
           <t>学校</t>
         </is>
       </c>
-      <c r="YD1" t="inlineStr">
+      <c r="YO1" t="inlineStr">
         <is>
           <t>医院</t>
         </is>
       </c>
-      <c r="YE1" t="inlineStr">
+      <c r="YP1" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="YF1" t="inlineStr">
+      <c r="YQ1" t="inlineStr">
         <is>
           <t>工程</t>
         </is>
       </c>
-      <c r="YG1" t="inlineStr">
+      <c r="YR1" t="inlineStr">
         <is>
           <t>标段</t>
         </is>
       </c>
-      <c r="YH1" t="inlineStr">
+      <c r="YS1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="YI1" t="inlineStr">
+      <c r="YT1" t="inlineStr">
         <is>
           <t>渠道</t>
         </is>
       </c>
-      <c r="YJ1" t="inlineStr">
+      <c r="YU1" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="YK1" t="inlineStr">
+      <c r="YV1" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="YL1" t="inlineStr">
+      <c r="YW1" t="inlineStr">
         <is>
           <t>地址</t>
         </is>
       </c>
-      <c r="YM1" t="inlineStr">
+      <c r="YX1" t="inlineStr">
         <is>
           <t>联系人</t>
         </is>
       </c>
-      <c r="YN1" t="inlineStr">
+      <c r="YY1" t="inlineStr">
         <is>
           <t>职务</t>
         </is>
       </c>
-      <c r="YO1" t="inlineStr">
+      <c r="YZ1" t="inlineStr">
         <is>
           <t>职业</t>
         </is>
       </c>
-      <c r="YP1" t="inlineStr">
+      <c r="ZA1" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="YQ1" t="inlineStr">
+      <c r="ZB1" t="inlineStr">
         <is>
           <t>课程</t>
         </is>
       </c>
-      <c r="YR1" t="inlineStr">
+      <c r="ZC1" t="inlineStr">
         <is>
           <t>标准</t>
         </is>
       </c>
-      <c r="YS1" t="inlineStr">
+      <c r="ZD1" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
-      <c r="YT1" t="inlineStr">
+      <c r="ZE1" t="inlineStr">
         <is>
           <t>方式</t>
         </is>
       </c>
-      <c r="YU1" t="inlineStr">
+      <c r="ZF1" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
       </c>
-      <c r="YV1" t="inlineStr">
+      <c r="ZG1" t="inlineStr">
         <is>
           <t>工艺</t>
         </is>
       </c>
-      <c r="YW1" t="inlineStr">
+      <c r="ZH1" t="inlineStr">
         <is>
           <t>工序</t>
         </is>
       </c>
-      <c r="YX1" t="inlineStr">
+      <c r="ZI1" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="YY1" t="inlineStr">
+      <c r="ZJ1" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="YZ1" t="inlineStr">
+      <c r="ZK1" t="inlineStr">
         <is>
           <t>称谓</t>
         </is>
       </c>
-      <c r="ZA1" t="inlineStr">
+      <c r="ZL1" t="inlineStr">
         <is>
           <t>职称</t>
         </is>
       </c>
-      <c r="ZB1" t="inlineStr">
+      <c r="ZM1" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="ZC1" t="inlineStr">
+      <c r="ZN1" t="inlineStr">
         <is>
           <t>职位</t>
         </is>
       </c>
-      <c r="ZD1" t="inlineStr">
+      <c r="ZO1" t="inlineStr">
         <is>
           <t>科室</t>
         </is>
       </c>
-      <c r="ZE1" t="inlineStr">
+      <c r="ZP1" t="inlineStr">
         <is>
           <t>班组</t>
         </is>
       </c>
-      <c r="ZF1" t="inlineStr">
+      <c r="ZQ1" t="inlineStr">
         <is>
           <t>班级</t>
         </is>
       </c>
-      <c r="ZG1" t="inlineStr">
+      <c r="ZR1" t="inlineStr">
         <is>
           <t>专业</t>
         </is>
       </c>
-      <c r="ZH1" t="inlineStr">
+      <c r="ZS1" t="inlineStr">
         <is>
           <t>院系</t>
         </is>
       </c>
-      <c r="ZI1" t="inlineStr">
+      <c r="ZT1" t="inlineStr">
         <is>
           <t>校区</t>
         </is>
       </c>
-      <c r="ZJ1" t="inlineStr">
+      <c r="ZU1" t="inlineStr">
         <is>
           <t>场馆</t>
         </is>
       </c>
-      <c r="ZK1" t="inlineStr">
+      <c r="ZV1" t="inlineStr">
         <is>
           <t>楼盘</t>
         </is>
       </c>
-      <c r="ZL1" t="inlineStr">
+      <c r="ZW1" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="ZM1" t="inlineStr">
+      <c r="ZX1" t="inlineStr">
         <is>
           <t>街道</t>
         </is>
       </c>
-      <c r="ZN1" t="inlineStr">
+      <c r="ZY1" t="inlineStr">
         <is>
           <t>社区</t>
         </is>
       </c>
-      <c r="ZO1" t="inlineStr">
+      <c r="ZZ1" t="inlineStr">
         <is>
           <t>村镇</t>
         </is>
       </c>
-      <c r="ZP1" t="inlineStr">
+      <c r="AAA1" t="inlineStr">
         <is>
           <t>路段</t>
         </is>
       </c>
-      <c r="ZQ1" t="inlineStr">
+      <c r="AAB1" t="inlineStr">
         <is>
           <t>线路</t>
         </is>
       </c>
-      <c r="ZR1" t="inlineStr">
+      <c r="AAC1" t="inlineStr">
         <is>
           <t>管线</t>
         </is>
       </c>
-      <c r="ZS1" t="inlineStr">
+      <c r="AAD1" t="inlineStr">
         <is>
           <t>站点</t>
         </is>
       </c>
-      <c r="ZT1" t="inlineStr">
+      <c r="AAE1" t="inlineStr">
         <is>
           <t>品名</t>
         </is>
       </c>
-      <c r="ZU1" t="inlineStr">
+      <c r="AAF1" t="inlineStr">
         <is>
           <t>别名</t>
         </is>
       </c>
-      <c r="ZV1" t="inlineStr">
+      <c r="AAG1" t="inlineStr">
         <is>
           <t>曾用名</t>
         </is>
       </c>
-      <c r="ZW1" t="inlineStr">
+      <c r="AAH1" t="inlineStr">
         <is>
           <t>简称</t>
         </is>
       </c>
-      <c r="ZX1" t="inlineStr">
+      <c r="AAI1" t="inlineStr">
         <is>
           <t>全称</t>
         </is>
       </c>
-      <c r="ZY1" t="inlineStr">
+      <c r="AAJ1" t="inlineStr">
         <is>
           <t>栏目</t>
         </is>
       </c>
-      <c r="ZZ1" t="inlineStr">
+      <c r="AAK1" t="inlineStr">
         <is>
           <t>频道</t>
         </is>
       </c>
-      <c r="AAA1" t="inlineStr">
+      <c r="AAL1" t="inlineStr">
         <is>
           <t>语种</t>
         </is>
       </c>
-      <c r="AAB1" t="inlineStr">
+      <c r="AAM1" t="inlineStr">
         <is>
           <t>币种</t>
         </is>
       </c>
-      <c r="AAC1" t="inlineStr">
+      <c r="AAN1" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="AAD1" t="inlineStr">
+      <c r="AAO1" t="inlineStr">
         <is>
           <t>经办人</t>
         </is>
       </c>
-      <c r="AAE1" t="inlineStr">
+      <c r="AAP1" t="inlineStr">
         <is>
           <t>审核人</t>
         </is>
       </c>
-      <c r="AAF1" t="inlineStr">
+      <c r="AAQ1" t="inlineStr">
         <is>
           <t>批准人</t>
         </is>
       </c>
-      <c r="AAG1" t="inlineStr">
+      <c r="AAR1" t="inlineStr">
         <is>
           <t>填报人</t>
         </is>
       </c>
-      <c r="AAH1" t="inlineStr">
+      <c r="AAS1" t="inlineStr">
         <is>
           <t>编制人</t>
         </is>
       </c>
-      <c r="AAI1" t="inlineStr">
+      <c r="AAT1" t="inlineStr">
         <is>
           <t>责任人</t>
         </is>
       </c>
-      <c r="AAJ1" t="inlineStr">
+      <c r="AAU1" t="inlineStr">
         <is>
           <t>申请人</t>
         </is>
       </c>
-      <c r="AAK1" t="inlineStr">
+      <c r="AAV1" t="inlineStr">
         <is>
           <t>受理人</t>
         </is>
       </c>
-      <c r="AAL1" t="inlineStr">
+      <c r="AAW1" t="inlineStr">
         <is>
           <t>创建人</t>
         </is>
       </c>
-      <c r="AAM1" t="inlineStr">
+      <c r="AAX1" t="inlineStr">
         <is>
           <t>修改人</t>
         </is>
       </c>
-      <c r="AAN1" t="inlineStr">
+      <c r="AAY1" t="inlineStr">
         <is>
           <t>更新人</t>
         </is>
       </c>
-      <c r="AAO1" t="inlineStr">
+      <c r="AAZ1" t="inlineStr">
         <is>
           <t>删除人</t>
         </is>
       </c>
-      <c r="AAP1" t="inlineStr">
+      <c r="ABA1" t="inlineStr">
         <is>
           <t>录入人</t>
         </is>
       </c>
-      <c r="AAQ1" t="inlineStr">
+      <c r="ABB1" t="inlineStr">
         <is>
           <t>制单人</t>
         </is>
       </c>
-      <c r="AAR1" t="inlineStr">
+      <c r="ABC1" t="inlineStr">
         <is>
           <t>复核人</t>
         </is>
       </c>
-      <c r="AAS1" t="inlineStr">
+      <c r="ABD1" t="inlineStr">
         <is>
           <t>移交人</t>
         </is>
       </c>
-      <c r="AAT1" t="inlineStr">
+      <c r="ABE1" t="inlineStr">
         <is>
           <t>接收人</t>
         </is>
       </c>
-      <c r="AAU1" t="inlineStr">
+      <c r="ABF1" t="inlineStr">
         <is>
           <t>密级</t>
         </is>
       </c>
-      <c r="AAV1" t="inlineStr">
+      <c r="ABG1" t="inlineStr">
         <is>
           <t>级别</t>
         </is>
       </c>
-      <c r="AAW1" t="inlineStr">
+      <c r="ABH1" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="AAX1" t="inlineStr">
+      <c r="ABI1" t="inlineStr">
         <is>
           <t>建制</t>
         </is>
       </c>
-      <c r="AAY1" t="inlineStr">
+      <c r="ABJ1" t="inlineStr">
         <is>
           <t>番号</t>
         </is>
       </c>
-      <c r="AAZ1" t="inlineStr">
+      <c r="ABK1" t="inlineStr">
         <is>
           <t>部队</t>
         </is>
       </c>
-      <c r="ABA1" t="inlineStr">
+      <c r="ABL1" t="inlineStr">
+        <is>
+          <t>课目</t>
+        </is>
+      </c>
+      <c r="ABM1" t="inlineStr">
+        <is>
+          <t>驾驶员</t>
+        </is>
+      </c>
+      <c r="ABN1" t="inlineStr">
+        <is>
+          <t>附件</t>
+        </is>
+      </c>
+      <c r="ABO1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="ABP1" t="inlineStr">
+        <is>
+          <t>标记</t>
+        </is>
+      </c>
+      <c r="ABQ1" t="inlineStr">
         <is>
           <t>网址</t>
         </is>
       </c>
-      <c r="ABB1" t="inlineStr">
+      <c r="ABR1" t="inlineStr">
         <is>
           <t>网站</t>
         </is>
       </c>
-      <c r="ABC1" t="inlineStr">
+      <c r="ABS1" t="inlineStr">
         <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="ABD1" t="inlineStr">
+      <c r="ABT1" t="inlineStr">
         <is>
           <t>超链接</t>
         </is>
       </c>
-      <c r="ABE1" t="inlineStr">
+      <c r="ABU1" t="inlineStr">
         <is>
           <t>路径</t>
         </is>
       </c>
-      <c r="ABF1" t="inlineStr">
+      <c r="ABV1" t="inlineStr">
         <is>
           <t>下载地址</t>
         </is>
       </c>
-      <c r="ABG1" t="inlineStr">
+      <c r="ABW1" t="inlineStr">
         <is>
           <t>访问地址</t>
         </is>
       </c>
-      <c r="ABH1" t="inlineStr">
+      <c r="ABX1" t="inlineStr">
         <is>
           <t>图片地址</t>
         </is>
       </c>
-      <c r="ABI1" t="inlineStr">
+      <c r="ABY1" t="inlineStr">
         <is>
           <t>附件地址</t>
         </is>
       </c>
-      <c r="ABJ1" t="inlineStr">
+      <c r="ABZ1" t="inlineStr">
         <is>
           <t>文件地址</t>
         </is>
       </c>
-      <c r="ABK1" t="inlineStr">
+      <c r="ACA1" t="inlineStr">
         <is>
           <t>主页</t>
         </is>
       </c>
-      <c r="ABL1" t="inlineStr">
+      <c r="ACB1" t="inlineStr">
         <is>
           <t>官网</t>
         </is>
       </c>
-      <c r="ABM1" t="inlineStr">
+      <c r="ACC1" t="inlineStr">
         <is>
           <t>域名</t>
         </is>
       </c>
-      <c r="ABN1" t="inlineStr">
+      <c r="ACD1" t="inlineStr">
         <is>
           <t>短链</t>
         </is>
       </c>
-      <c r="ABO1" t="inlineStr">
+      <c r="ACE1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="ABP1" t="inlineStr">
+      <c r="ACF1" t="inlineStr">
         <is>
           <t>amt</t>
         </is>
       </c>
-      <c r="ABQ1" t="inlineStr">
+      <c r="ACG1" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="ABR1" t="inlineStr">
+      <c r="ACH1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="ABS1" t="inlineStr">
+      <c r="ACI1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="ABT1" t="inlineStr">
+      <c r="ACJ1" t="inlineStr">
         <is>
           <t>fee</t>
         </is>
       </c>
-      <c r="ABU1" t="inlineStr">
+      <c r="ACK1" t="inlineStr">
         <is>
           <t>fees</t>
         </is>
       </c>
-      <c r="ABV1" t="inlineStr">
+      <c r="ACL1" t="inlineStr">
         <is>
           <t>salary</t>
         </is>
       </c>
-      <c r="ABW1" t="inlineStr">
+      <c r="ACM1" t="inlineStr">
         <is>
           <t>wage</t>
         </is>
       </c>
-      <c r="ABX1" t="inlineStr">
+      <c r="ACN1" t="inlineStr">
         <is>
           <t>wages</t>
         </is>
       </c>
-      <c r="ABY1" t="inlineStr">
+      <c r="ACO1" t="inlineStr">
         <is>
           <t>income</t>
         </is>
       </c>
-      <c r="ABZ1" t="inlineStr">
+      <c r="ACP1" t="inlineStr">
         <is>
           <t>expense</t>
         </is>
       </c>
-      <c r="ACA1" t="inlineStr">
+      <c r="ACQ1" t="inlineStr">
         <is>
           <t>expenses</t>
         </is>
       </c>
-      <c r="ACB1" t="inlineStr">
+      <c r="ACR1" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="ACC1" t="inlineStr">
+      <c r="ACS1" t="inlineStr">
         <is>
           <t>budget</t>
         </is>
       </c>
-      <c r="ACD1" t="inlineStr">
+      <c r="ACT1" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="ACE1" t="inlineStr">
+      <c r="ACU1" t="inlineStr">
         <is>
           <t>profit</t>
         </is>
       </c>
-      <c r="ACF1" t="inlineStr">
+      <c r="ACV1" t="inlineStr">
         <is>
           <t>payment</t>
         </is>
       </c>
-      <c r="ACG1" t="inlineStr">
+      <c r="ACW1" t="inlineStr">
         <is>
           <t>payable</t>
         </is>
       </c>
-      <c r="ACH1" t="inlineStr">
+      <c r="ACX1" t="inlineStr">
         <is>
           <t>receivable</t>
         </is>
       </c>
-      <c r="ACI1" t="inlineStr">
+      <c r="ACY1" t="inlineStr">
         <is>
           <t>charge</t>
         </is>
       </c>
-      <c r="ACJ1" t="inlineStr">
+      <c r="ACZ1" t="inlineStr">
         <is>
           <t>charges</t>
         </is>
       </c>
-      <c r="ACK1" t="inlineStr">
+      <c r="ADA1" t="inlineStr">
         <is>
           <t>fund</t>
         </is>
       </c>
-      <c r="ACL1" t="inlineStr">
+      <c r="ADB1" t="inlineStr">
         <is>
           <t>funds</t>
         </is>
       </c>
-      <c r="ACM1" t="inlineStr">
+      <c r="ADC1" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="ACN1" t="inlineStr">
+      <c r="ADD1" t="inlineStr">
         <is>
           <t>interest</t>
         </is>
       </c>
-      <c r="ACO1" t="inlineStr">
+      <c r="ADE1" t="inlineStr">
         <is>
           <t>capital</t>
         </is>
       </c>
-      <c r="ACP1" t="inlineStr">
+      <c r="ADF1" t="inlineStr">
         <is>
           <t>pay</t>
         </is>
       </c>
-      <c r="ACQ1" t="inlineStr">
+      <c r="ADG1" t="inlineStr">
         <is>
           <t>fare</t>
         </is>
       </c>
-      <c r="ACR1" t="inlineStr">
+      <c r="ADH1" t="inlineStr">
         <is>
           <t>toll</t>
         </is>
       </c>
-      <c r="ACS1" t="inlineStr">
+      <c r="ADI1" t="inlineStr">
         <is>
           <t>refund</t>
         </is>
       </c>
-      <c r="ACT1" t="inlineStr">
+      <c r="ADJ1" t="inlineStr">
         <is>
           <t>deposit</t>
         </is>
       </c>
-      <c r="ACU1" t="inlineStr">
+      <c r="ADK1" t="inlineStr">
         <is>
           <t>fine</t>
         </is>
       </c>
-      <c r="ACV1" t="inlineStr">
+      <c r="ADL1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="ACW1" t="inlineStr">
+      <c r="ADM1" t="inlineStr">
         <is>
           <t>royalty</t>
         </is>
       </c>
-      <c r="ACX1" t="inlineStr">
+      <c r="ADN1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>
       </c>
-      <c r="ACY1" t="inlineStr">
+      <c r="ADO1" t="inlineStr">
         <is>
           <t>dividend</t>
         </is>
       </c>
-      <c r="ACZ1" t="inlineStr">
+      <c r="ADP1" t="inlineStr">
         <is>
           <t>bonus</t>
         </is>
       </c>
-      <c r="ADA1" t="inlineStr">
+      <c r="ADQ1" t="inlineStr">
         <is>
           <t>subsidy</t>
         </is>
       </c>
-      <c r="ADB1" t="inlineStr">
+      <c r="ADR1" t="inlineStr">
         <is>
           <t>allowance</t>
         </is>
       </c>
-      <c r="ADC1" t="inlineStr">
+      <c r="ADS1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="ADD1" t="inlineStr">
+      <c r="ADT1" t="inlineStr">
         <is>
           <t>earnings</t>
         </is>
       </c>
-      <c r="ADE1" t="inlineStr">
+      <c r="ADU1" t="inlineStr">
         <is>
           <t>turnover</t>
         </is>
       </c>
-      <c r="ADF1" t="inlineStr">
+      <c r="ADV1" t="inlineStr">
         <is>
           <t>rent</t>
         </is>
       </c>
-      <c r="ADG1" t="inlineStr">
+      <c r="ADW1" t="inlineStr">
         <is>
           <t>loan</t>
         </is>
       </c>
-      <c r="ADH1" t="inlineStr">
+      <c r="ADX1" t="inlineStr">
         <is>
           <t>mortgage</t>
         </is>
       </c>
-      <c r="ADI1" t="inlineStr">
+      <c r="ADY1" t="inlineStr">
         <is>
           <t>arrears</t>
         </is>
       </c>
-      <c r="ADJ1" t="inlineStr">
+      <c r="ADZ1" t="inlineStr">
         <is>
           <t>receipt</t>
         </is>
       </c>
-      <c r="ADK1" t="inlineStr">
+      <c r="AEA1" t="inlineStr">
         <is>
           <t>receipts</t>
         </is>
       </c>
-      <c r="ADL1" t="inlineStr">
+      <c r="AEB1" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="ADM1" t="inlineStr">
+      <c r="AEC1" t="inlineStr">
         <is>
           <t>disbursement</t>
         </is>
       </c>
-      <c r="ADN1" t="inlineStr">
+      <c r="AED1" t="inlineStr">
         <is>
           <t>expenditure</t>
         </is>
       </c>
-      <c r="ADO1" t="inlineStr">
+      <c r="AEE1" t="inlineStr">
         <is>
           <t>spending</t>
         </is>
       </c>
-      <c r="ADP1" t="inlineStr">
+      <c r="AEF1" t="inlineStr">
         <is>
           <t>worth</t>
         </is>
       </c>
-      <c r="ADQ1" t="inlineStr">
+      <c r="AEG1" t="inlineStr">
         <is>
           <t>valuation</t>
         </is>
       </c>
-      <c r="ADR1" t="inlineStr">
+      <c r="AEH1" t="inlineStr">
         <is>
           <t>equity</t>
         </is>
       </c>
-      <c r="ADS1" t="inlineStr">
+      <c r="AEI1" t="inlineStr">
         <is>
           <t>dues</t>
         </is>
       </c>
-      <c r="ADT1" t="inlineStr">
+      <c r="AEJ1" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="ADU1" t="inlineStr">
+      <c r="AEK1" t="inlineStr">
         <is>
           <t>installment</t>
         </is>
       </c>
-      <c r="ADV1" t="inlineStr">
+      <c r="AEL1" t="inlineStr">
         <is>
           <t>prepayment</t>
         </is>
       </c>
-      <c r="ADW1" t="inlineStr">
+      <c r="AEM1" t="inlineStr">
         <is>
           <t>deductible</t>
         </is>
       </c>
-      <c r="ADX1" t="inlineStr">
+      <c r="AEN1" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="ADY1" t="inlineStr">
+      <c r="AEO1" t="inlineStr">
         <is>
           <t>premium</t>
         </is>
       </c>
-      <c r="ADZ1" t="inlineStr">
+      <c r="AEP1" t="inlineStr">
         <is>
           <t>reimbursement</t>
         </is>
       </c>
-      <c r="AEA1" t="inlineStr">
+      <c r="AEQ1" t="inlineStr">
         <is>
           <t>stipend</t>
         </is>
       </c>
-      <c r="AEB1" t="inlineStr">
+      <c r="AER1" t="inlineStr">
         <is>
           <t>honorarium</t>
         </is>
       </c>
-      <c r="AEC1" t="inlineStr">
+      <c r="AES1" t="inlineStr">
         <is>
           <t>gratuity</t>
         </is>
       </c>
-      <c r="AED1" t="inlineStr">
+      <c r="AET1" t="inlineStr">
         <is>
           <t>payout</t>
         </is>
       </c>
-      <c r="AEE1" t="inlineStr">
+      <c r="AEU1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="AEF1" t="inlineStr">
+      <c r="AEV1" t="inlineStr">
         <is>
           <t>views</t>
         </is>
       </c>
-      <c r="AEG1" t="inlineStr">
+      <c r="AEW1" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
       </c>
-      <c r="AEH1" t="inlineStr">
+      <c r="AEX1" t="inlineStr">
         <is>
           <t>clicks</t>
         </is>
       </c>
-      <c r="AEI1" t="inlineStr">
+      <c r="AEY1" t="inlineStr">
         <is>
           <t>downloads</t>
         </is>
       </c>
-      <c r="AEJ1" t="inlineStr">
+      <c r="AEZ1" t="inlineStr">
         <is>
           <t>plays</t>
         </is>
       </c>
-      <c r="AEK1" t="inlineStr">
+      <c r="AFA1" t="inlineStr">
         <is>
           <t>impressions</t>
         </is>
       </c>
-      <c r="AEL1" t="inlineStr">
+      <c r="AFB1" t="inlineStr">
         <is>
           <t>pageviews</t>
         </is>
       </c>
-      <c r="AEM1" t="inlineStr">
+      <c r="AFC1" t="inlineStr">
         <is>
           <t>followers</t>
         </is>
       </c>
-      <c r="AEN1" t="inlineStr">
+      <c r="AFD1" t="inlineStr">
         <is>
           <t>fans</t>
         </is>
       </c>
-      <c r="AEO1" t="inlineStr">
+      <c r="AFE1" t="inlineStr">
         <is>
           <t>likes</t>
         </is>
       </c>
-      <c r="AEP1" t="inlineStr">
+      <c r="AFF1" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="AEQ1" t="inlineStr">
+      <c r="AFG1" t="inlineStr">
         <is>
           <t>shares</t>
         </is>
       </c>
-      <c r="AER1" t="inlineStr">
+      <c r="AFH1" t="inlineStr">
         <is>
           <t>is</t>
         </is>
       </c>
-      <c r="AES1" t="inlineStr">
+      <c r="AFI1" t="inlineStr">
         <is>
           <t>has</t>
         </is>
       </c>
-      <c r="AET1" t="inlineStr">
+      <c r="AFJ1" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="AEU1" t="inlineStr">
+      <c r="AFK1" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="AEV1" t="inlineStr">
+      <c r="AFL1" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
       </c>
-      <c r="AEW1" t="inlineStr">
+      <c r="AFM1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="AEX1" t="inlineStr">
+      <c r="AFN1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AEY1" t="inlineStr">
+      <c r="AFO1" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="AEZ1" t="inlineStr">
+      <c r="AFP1" t="inlineStr">
         <is>
           <t>deleted</t>
         </is>
       </c>
-      <c r="AFA1" t="inlineStr">
+      <c r="AFQ1" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="AFB1" t="inlineStr">
+      <c r="AFR1" t="inlineStr">
         <is>
           <t>yn</t>
         </is>
       </c>
-      <c r="AFC1" t="inlineStr">
+      <c r="AFS1" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="AFD1" t="inlineStr">
+      <c r="AFT1" t="inlineStr">
         <is>
           <t>allowed</t>
         </is>
       </c>
-      <c r="AFE1" t="inlineStr">
+      <c r="AFU1" t="inlineStr">
         <is>
           <t>need</t>
         </is>
       </c>
-      <c r="AFF1" t="inlineStr">
+      <c r="AFV1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="AFG1" t="inlineStr">
+      <c r="AFW1" t="inlineStr">
         <is>
           <t>checked</t>
         </is>
       </c>
-      <c r="AFH1" t="inlineStr">
+      <c r="AFX1" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="AFI1" t="inlineStr">
+      <c r="AFY1" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="AFJ1" t="inlineStr">
+      <c r="AFZ1" t="inlineStr">
         <is>
           <t>locked</t>
         </is>
       </c>
-      <c r="AFK1" t="inlineStr">
+      <c r="AGA1" t="inlineStr">
         <is>
           <t>visible</t>
         </is>
       </c>
-      <c r="AFL1" t="inlineStr">
+      <c r="AGB1" t="inlineStr">
         <is>
           <t>available</t>
         </is>
       </c>
-      <c r="AFM1" t="inlineStr">
+      <c r="AGC1" t="inlineStr">
         <is>
           <t>permitted</t>
         </is>
       </c>
-      <c r="AFN1" t="inlineStr">
+      <c r="AGD1" t="inlineStr">
         <is>
           <t>yesno</t>
         </is>
       </c>
-      <c r="AFO1" t="inlineStr">
+      <c r="AGE1" t="inlineStr">
         <is>
           <t>truefalse</t>
         </is>
       </c>
-      <c r="AFP1" t="inlineStr">
+      <c r="AGF1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="AFQ1" t="inlineStr">
+      <c r="AGG1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="AFR1" t="inlineStr">
+      <c r="AGH1" t="inlineStr">
         <is>
           <t>quarter</t>
         </is>
       </c>
-      <c r="AFS1" t="inlineStr">
+      <c r="AGI1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="AFT1" t="inlineStr">
+      <c r="AGJ1" t="inlineStr">
         <is>
           <t>hour</t>
         </is>
       </c>
-      <c r="AFU1" t="inlineStr">
+      <c r="AGK1" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="AFV1" t="inlineStr">
+      <c r="AGL1" t="inlineStr">
         <is>
           <t>second</t>
         </is>
       </c>
-      <c r="AFW1" t="inlineStr">
+      <c r="AGM1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="AFX1" t="inlineStr">
+      <c r="AGN1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="AFY1" t="inlineStr">
+      <c r="AGO1" t="inlineStr">
         <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="AFZ1" t="inlineStr">
+      <c r="AGP1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="AGA1" t="inlineStr">
+      <c r="AGQ1" t="inlineStr">
         <is>
           <t>lon</t>
         </is>
       </c>
-      <c r="AGB1" t="inlineStr">
+      <c r="AGR1" t="inlineStr">
         <is>
           <t>coord</t>
         </is>
       </c>
-      <c r="AGC1" t="inlineStr">
+      <c r="AGS1" t="inlineStr">
         <is>
           <t>coords</t>
         </is>
       </c>
-      <c r="AGD1" t="inlineStr">
+      <c r="AGT1" t="inlineStr">
         <is>
           <t>coordinate</t>
         </is>
       </c>
-      <c r="AGE1" t="inlineStr">
+      <c r="AGU1" t="inlineStr">
         <is>
           <t>gps</t>
         </is>
       </c>
-      <c r="AGF1" t="inlineStr">
+      <c r="AGV1" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="AGG1" t="inlineStr">
+      <c r="AGW1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="AGH1" t="inlineStr">
+      <c r="AGX1" t="inlineStr">
         <is>
           <t>dt</t>
         </is>
       </c>
-      <c r="AGI1" t="inlineStr">
+      <c r="AGY1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="AGJ1" t="inlineStr">
+      <c r="AGZ1" t="inlineStr">
         <is>
           <t>elapsed</t>
         </is>
       </c>
-      <c r="AGK1" t="inlineStr">
+      <c r="AHA1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="AGL1" t="inlineStr">
+      <c r="AHB1" t="inlineStr">
         <is>
           <t>latency</t>
         </is>
       </c>
-      <c r="AGM1" t="inlineStr">
+      <c r="AHC1" t="inlineStr">
         <is>
           <t>qty</t>
         </is>
       </c>
-      <c r="AGN1" t="inlineStr">
+      <c r="AHD1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="AGO1" t="inlineStr">
+      <c r="AHE1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AGP1" t="inlineStr">
+      <c r="AHF1" t="inlineStr">
         <is>
           <t>cnt</t>
         </is>
       </c>
-      <c r="AGQ1" t="inlineStr">
+      <c r="AHG1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="AGR1" t="inlineStr">
+      <c r="AHH1" t="inlineStr">
         <is>
           <t>members</t>
         </is>
       </c>
-      <c r="AGS1" t="inlineStr">
+      <c r="AHI1" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="AGT1" t="inlineStr">
+      <c r="AHJ1" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
-      <c r="AGU1" t="inlineStr">
+      <c r="AHK1" t="inlineStr">
         <is>
           <t>pieces</t>
         </is>
       </c>
-      <c r="AGV1" t="inlineStr">
+      <c r="AHL1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="AGW1" t="inlineStr">
+      <c r="AHM1" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="AGX1" t="inlineStr">
+      <c r="AHN1" t="inlineStr">
         <is>
           <t>height</t>
         </is>
       </c>
-      <c r="AGY1" t="inlineStr">
+      <c r="AHO1" t="inlineStr">
         <is>
           <t>thickness</t>
         </is>
       </c>
-      <c r="AGZ1" t="inlineStr">
+      <c r="AHP1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AHA1" t="inlineStr">
+      <c r="AHQ1" t="inlineStr">
         <is>
           <t>distance</t>
         </is>
       </c>
-      <c r="AHB1" t="inlineStr">
+      <c r="AHR1" t="inlineStr">
         <is>
           <t>mileage</t>
         </is>
       </c>
-      <c r="AHC1" t="inlineStr">
+      <c r="AHS1" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="AHD1" t="inlineStr">
+      <c r="AHT1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AHE1" t="inlineStr">
+      <c r="AHU1" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="AHF1" t="inlineStr">
+      <c r="AHV1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="AHG1" t="inlineStr">
+      <c r="AHW1" t="inlineStr">
         <is>
           <t>temperature</t>
         </is>
       </c>
-      <c r="AHH1" t="inlineStr">
+      <c r="AHX1" t="inlineStr">
         <is>
           <t>humidity</t>
         </is>
       </c>
-      <c r="AHI1" t="inlineStr">
+      <c r="AHY1" t="inlineStr">
         <is>
           <t>density</t>
         </is>
       </c>
-      <c r="AHJ1" t="inlineStr">
+      <c r="AHZ1" t="inlineStr">
         <is>
           <t>pressure</t>
         </is>
       </c>
-      <c r="AHK1" t="inlineStr">
+      <c r="AIA1" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="AHL1" t="inlineStr">
+      <c r="AIB1" t="inlineStr">
         <is>
           <t>flow</t>
         </is>
       </c>
-      <c r="AHM1" t="inlineStr">
+      <c r="AIC1" t="inlineStr">
         <is>
           <t>power</t>
         </is>
       </c>
-      <c r="AHN1" t="inlineStr">
+      <c r="AID1" t="inlineStr">
         <is>
           <t>voltage</t>
         </is>
       </c>
-      <c r="AHO1" t="inlineStr">
+      <c r="AIE1" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="AHP1" t="inlineStr">
+      <c r="AIF1" t="inlineStr">
         <is>
           <t>elevation</t>
         </is>
       </c>
-      <c r="AHQ1" t="inlineStr">
+      <c r="AIG1" t="inlineStr">
         <is>
           <t>altitude</t>
         </is>
       </c>
-      <c r="AHR1" t="inlineStr">
+      <c r="AIH1" t="inlineStr">
         <is>
           <t>diameter</t>
         </is>
       </c>
-      <c r="AHS1" t="inlineStr">
+      <c r="AII1" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="AHT1" t="inlineStr">
+      <c r="AIJ1" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="AHU1" t="inlineStr">
+      <c r="AIK1" t="inlineStr">
         <is>
           <t>span</t>
         </is>
       </c>
-      <c r="AHV1" t="inlineStr">
+      <c r="AIL1" t="inlineStr">
         <is>
           <t>spacing</t>
         </is>
       </c>
-      <c r="AHW1" t="inlineStr">
+      <c r="AIM1" t="inlineStr">
         <is>
           <t>slope</t>
         </is>
       </c>
-      <c r="AHX1" t="inlineStr">
+      <c r="AIN1" t="inlineStr">
         <is>
           <t>hardness</t>
         </is>
       </c>
-      <c r="AHY1" t="inlineStr">
+      <c r="AIO1" t="inlineStr">
         <is>
           <t>strength</t>
         </is>
       </c>
-      <c r="AHZ1" t="inlineStr">
+      <c r="AIP1" t="inlineStr">
         <is>
           <t>stress</t>
         </is>
       </c>
-      <c r="AIA1" t="inlineStr">
+      <c r="AIQ1" t="inlineStr">
         <is>
           <t>strain</t>
         </is>
       </c>
-      <c r="AIB1" t="inlineStr">
+      <c r="AIR1" t="inlineStr">
         <is>
           <t>modulus</t>
         </is>
       </c>
-      <c r="AIC1" t="inlineStr">
+      <c r="AIS1" t="inlineStr">
         <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="AID1" t="inlineStr">
+      <c r="AIT1" t="inlineStr">
         <is>
           <t>capacitance</t>
         </is>
       </c>
-      <c r="AIE1" t="inlineStr">
+      <c r="AIU1" t="inlineStr">
         <is>
           <t>inductance</t>
         </is>
       </c>
-      <c r="AIF1" t="inlineStr">
+      <c r="AIV1" t="inlineStr">
         <is>
           <t>impedance</t>
         </is>
       </c>
-      <c r="AIG1" t="inlineStr">
+      <c r="AIW1" t="inlineStr">
         <is>
           <t>consumption</t>
         </is>
       </c>
-      <c r="AIH1" t="inlineStr">
+      <c r="AIX1" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="AII1" t="inlineStr">
+      <c r="AIY1" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="AIJ1" t="inlineStr">
+      <c r="AIZ1" t="inlineStr">
         <is>
           <t>velocity</t>
         </is>
       </c>
-      <c r="AIK1" t="inlineStr">
+      <c r="AJA1" t="inlineStr">
         <is>
           <t>torque</t>
         </is>
       </c>
-      <c r="AIL1" t="inlineStr">
+      <c r="AJB1" t="inlineStr">
         <is>
           <t>brightness</t>
         </is>
       </c>
-      <c r="AIM1" t="inlineStr">
+      <c r="AJC1" t="inlineStr">
         <is>
           <t>amplitude</t>
         </is>
       </c>
-      <c r="AIN1" t="inlineStr">
+      <c r="AJD1" t="inlineStr">
         <is>
           <t>deflection</t>
         </is>
       </c>
-      <c r="AIO1" t="inlineStr">
+      <c r="AJE1" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AIP1" t="inlineStr">
+      <c r="AJF1" t="inlineStr">
         <is>
           <t>displacement</t>
         </is>
       </c>
-      <c r="AIQ1" t="inlineStr">
+      <c r="AJG1" t="inlineStr">
         <is>
           <t>noise</t>
         </is>
       </c>
-      <c r="AIR1" t="inlineStr">
+      <c r="AJH1" t="inlineStr">
         <is>
           <t>decibel</t>
         </is>
       </c>
-      <c r="AIS1" t="inlineStr">
+      <c r="AJI1" t="inlineStr">
         <is>
           <t>radiation</t>
         </is>
       </c>
-      <c r="AIT1" t="inlineStr">
+      <c r="AJJ1" t="inlineStr">
         <is>
           <t>clearance</t>
         </is>
       </c>
-      <c r="AIU1" t="inlineStr">
+      <c r="AJK1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="AIV1" t="inlineStr">
+      <c r="AJL1" t="inlineStr">
         <is>
           <t>ranking</t>
         </is>
       </c>
-      <c r="AIW1" t="inlineStr">
+      <c r="AJM1" t="inlineStr">
         <is>
           <t>sort</t>
         </is>
       </c>
-      <c r="AIX1" t="inlineStr">
+      <c r="AJN1" t="inlineStr">
         <is>
           <t>seq</t>
         </is>
       </c>
-      <c r="AIY1" t="inlineStr">
+      <c r="AJO1" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="AIZ1" t="inlineStr">
+      <c r="AJP1" t="inlineStr">
         <is>
           <t>serial</t>
         </is>
       </c>
-      <c r="AJA1" t="inlineStr">
+      <c r="AJQ1" t="inlineStr">
         <is>
           <t>page</t>
         </is>
       </c>
-      <c r="AJB1" t="inlineStr">
+      <c r="AJR1" t="inlineStr">
         <is>
           <t>pages</t>
         </is>
       </c>
-      <c r="AJC1" t="inlineStr">
+      <c r="AJS1" t="inlineStr">
         <is>
           <t>floor</t>
         </is>
       </c>
-      <c r="AJD1" t="inlineStr">
+      <c r="AJT1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="AJE1" t="inlineStr">
+      <c r="AJU1" t="inlineStr">
         <is>
           <t>ordinal</t>
         </is>
       </c>
-      <c r="AJF1" t="inlineStr">
+      <c r="AJV1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="AJG1" t="inlineStr">
+      <c r="AJW1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="AJH1" t="inlineStr">
+      <c r="AJX1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="AJI1" t="inlineStr">
+      <c r="AJY1" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="AJJ1" t="inlineStr">
+      <c r="AJZ1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
       </c>
-      <c r="AJK1" t="inlineStr">
+      <c r="AKA1" t="inlineStr">
         <is>
           <t>coefficient</t>
         </is>
       </c>
-      <c r="AJL1" t="inlineStr">
+      <c r="AKB1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="AJM1" t="inlineStr">
+      <c r="AKC1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AJN1" t="inlineStr">
+      <c r="AKD1" t="inlineStr">
         <is>
           <t>discount</t>
         </is>
       </c>
-      <c r="AJO1" t="inlineStr">
+      <c r="AKE1" t="inlineStr">
         <is>
           <t>proportion</t>
         </is>
       </c>
-      <c r="AJP1" t="inlineStr">
+      <c r="AKF1" t="inlineStr">
         <is>
           <t>probability</t>
         </is>
       </c>
-      <c r="AJQ1" t="inlineStr">
+      <c r="AKG1" t="inlineStr">
         <is>
           <t>likelihood</t>
         </is>
       </c>
-      <c r="AJR1" t="inlineStr">
+      <c r="AKH1" t="inlineStr">
         <is>
           <t>permille</t>
         </is>
       </c>
-      <c r="AJS1" t="inlineStr">
+      <c r="AKI1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AJT1" t="inlineStr">
+      <c r="AKJ1" t="inlineStr">
         <is>
           <t>gpa</t>
         </is>
       </c>
-      <c r="AJU1" t="inlineStr">
+      <c r="AKK1" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="AJV1" t="inlineStr">
+      <c r="AKL1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="AJW1" t="inlineStr">
+      <c r="AKM1" t="inlineStr">
         <is>
           <t>ratings</t>
         </is>
       </c>
-      <c r="AJX1" t="inlineStr">
+      <c r="AKN1" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="AJY1" t="inlineStr">
+      <c r="AKO1" t="inlineStr">
         <is>
           <t>totals</t>
         </is>
       </c>
-      <c r="AJZ1" t="inlineStr">
+      <c r="AKP1" t="inlineStr">
         <is>
           <t>subtotal</t>
         </is>
       </c>
-      <c r="AKA1" t="inlineStr">
+      <c r="AKQ1" t="inlineStr">
         <is>
           <t>subtotals</t>
         </is>
       </c>
-      <c r="AKB1" t="inlineStr">
+      <c r="AKR1" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="AKC1" t="inlineStr">
+      <c r="AKS1" t="inlineStr">
         <is>
           <t>sums</t>
         </is>
       </c>
-      <c r="AKD1" t="inlineStr">
+      <c r="AKT1" t="inlineStr">
         <is>
           <t>aggregate</t>
         </is>
       </c>
-      <c r="AKE1" t="inlineStr">
+      <c r="AKU1" t="inlineStr">
         <is>
           <t>aggregates</t>
         </is>
       </c>
-      <c r="AKF1" t="inlineStr">
+      <c r="AKV1" t="inlineStr">
         <is>
           <t>cumulative</t>
         </is>
       </c>
-      <c r="AKG1" t="inlineStr">
+      <c r="AKW1" t="inlineStr">
         <is>
           <t>accumulation</t>
         </is>
       </c>
-      <c r="AKH1" t="inlineStr">
+      <c r="AKX1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
-      <c r="AKI1" t="inlineStr">
+      <c r="AKY1" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="AKJ1" t="inlineStr">
+      <c r="AKZ1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="AKK1" t="inlineStr">
+      <c r="ALA1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="AKL1" t="inlineStr">
+      <c r="ALB1" t="inlineStr">
         <is>
           <t>memo</t>
         </is>
       </c>
-      <c r="AKM1" t="inlineStr">
+      <c r="ALC1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AKN1" t="inlineStr">
+      <c r="ALD1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="AKO1" t="inlineStr">
+      <c r="ALE1" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="AKP1" t="inlineStr">
+      <c r="ALF1" t="inlineStr">
         <is>
           <t>details</t>
         </is>
       </c>
-      <c r="AKQ1" t="inlineStr">
+      <c r="ALG1" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
-      <c r="AKR1" t="inlineStr">
+      <c r="ALH1" t="inlineStr">
         <is>
           <t>contents</t>
         </is>
       </c>
-      <c r="AKS1" t="inlineStr">
+      <c r="ALI1" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="AKT1" t="inlineStr">
+      <c r="ALJ1" t="inlineStr">
         <is>
           <t>abstract</t>
         </is>
       </c>
-      <c r="AKU1" t="inlineStr">
+      <c r="ALK1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="AKV1" t="inlineStr">
+      <c r="ALL1" t="inlineStr">
         <is>
           <t>feedback</t>
         </is>
       </c>
-      <c r="AKW1" t="inlineStr">
+      <c r="ALM1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="AKX1" t="inlineStr">
+      <c r="ALN1" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="AKY1" t="inlineStr">
+      <c r="ALO1" t="inlineStr">
         <is>
           <t>intro</t>
         </is>
       </c>
-      <c r="AKZ1" t="inlineStr">
+      <c r="ALP1" t="inlineStr">
         <is>
           <t>introduction</t>
         </is>
       </c>
-      <c r="ALA1" t="inlineStr">
+      <c r="ALQ1" t="inlineStr">
         <is>
           <t>overview</t>
         </is>
       </c>
-      <c r="ALB1" t="inlineStr">
+      <c r="ALR1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
       </c>
-      <c r="ALC1" t="inlineStr">
+      <c r="ALS1" t="inlineStr">
         <is>
           <t>suggestion</t>
         </is>
       </c>
-      <c r="ALD1" t="inlineStr">
+      <c r="ALT1" t="inlineStr">
         <is>
           <t>suggestions</t>
         </is>
       </c>
-      <c r="ALE1" t="inlineStr">
+      <c r="ALU1" t="inlineStr">
         <is>
           <t>requirement</t>
         </is>
       </c>
-      <c r="ALF1" t="inlineStr">
+      <c r="ALV1" t="inlineStr">
         <is>
           <t>requirements</t>
         </is>
       </c>
-      <c r="ALG1" t="inlineStr">
+      <c r="ALW1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="ALH1" t="inlineStr">
+      <c r="ALX1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="ALI1" t="inlineStr">
+      <c r="ALY1" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="ALJ1" t="inlineStr">
+      <c r="ALZ1" t="inlineStr">
         <is>
           <t>advantage</t>
         </is>
       </c>
-      <c r="ALK1" t="inlineStr">
+      <c r="AMA1" t="inlineStr">
         <is>
           <t>advantages</t>
         </is>
       </c>
-      <c r="ALL1" t="inlineStr">
+      <c r="AMB1" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="ALM1" t="inlineStr">
+      <c r="AMC1" t="inlineStr">
         <is>
           <t>messages</t>
         </is>
       </c>
-      <c r="ALN1" t="inlineStr">
+      <c r="AMD1" t="inlineStr">
         <is>
           <t>statement</t>
         </is>
       </c>
-      <c r="ALO1" t="inlineStr">
+      <c r="AME1" t="inlineStr">
         <is>
           <t>statements</t>
         </is>
       </c>
-      <c r="ALP1" t="inlineStr">
+      <c r="AMF1" t="inlineStr">
         <is>
           <t>annotation</t>
         </is>
       </c>
-      <c r="ALQ1" t="inlineStr">
+      <c r="AMG1" t="inlineStr">
         <is>
           <t>annotations</t>
         </is>
       </c>
-      <c r="ALR1" t="inlineStr">
+      <c r="AMH1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="ALS1" t="inlineStr">
+      <c r="AMI1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="ALT1" t="inlineStr">
+      <c r="AMJ1" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="ALU1" t="inlineStr">
+      <c r="AMK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="ALV1" t="inlineStr">
+      <c r="AML1" t="inlineStr">
         <is>
           <t>names</t>
         </is>
       </c>
-      <c r="ALW1" t="inlineStr">
+      <c r="AMM1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="ALX1" t="inlineStr">
+      <c r="AMN1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="ALY1" t="inlineStr">
+      <c r="AMO1" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="ALZ1" t="inlineStr">
+      <c r="AMP1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AMA1" t="inlineStr">
+      <c r="AMQ1" t="inlineStr">
         <is>
           <t>types</t>
         </is>
       </c>
-      <c r="AMB1" t="inlineStr">
+      <c r="AMR1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="AMC1" t="inlineStr">
+      <c r="AMS1" t="inlineStr">
         <is>
           <t>kinds</t>
         </is>
       </c>
-      <c r="AMD1" t="inlineStr">
+      <c r="AMT1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="AME1" t="inlineStr">
+      <c r="AMU1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="AMF1" t="inlineStr">
+      <c r="AMV1" t="inlineStr">
         <is>
           <t>spec</t>
         </is>
       </c>
-      <c r="AMG1" t="inlineStr">
+      <c r="AMW1" t="inlineStr">
         <is>
           <t>specs</t>
         </is>
       </c>
-      <c r="AMH1" t="inlineStr">
+      <c r="AMX1" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="AMI1" t="inlineStr">
+      <c r="AMY1" t="inlineStr">
         <is>
           <t>color</t>
         </is>
       </c>
-      <c r="AMJ1" t="inlineStr">
+      <c r="AMZ1" t="inlineStr">
         <is>
           <t>colour</t>
         </is>
       </c>
-      <c r="AMK1" t="inlineStr">
+      <c r="ANA1" t="inlineStr">
         <is>
           <t>dept</t>
         </is>
       </c>
-      <c r="AML1" t="inlineStr">
+      <c r="ANB1" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="AMM1" t="inlineStr">
+      <c r="ANC1" t="inlineStr">
         <is>
           <t>organization</t>
         </is>
       </c>
-      <c r="AMN1" t="inlineStr">
+      <c r="AND1" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="AMO1" t="inlineStr">
+      <c r="ANE1" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="AMP1" t="inlineStr">
+      <c r="ANF1" t="inlineStr">
         <is>
           <t>school</t>
         </is>
       </c>
-      <c r="AMQ1" t="inlineStr">
+      <c r="ANG1" t="inlineStr">
         <is>
           <t>hospital</t>
         </is>
       </c>
-      <c r="AMR1" t="inlineStr">
+      <c r="ANH1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AMS1" t="inlineStr">
+      <c r="ANI1" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
       </c>
-      <c r="AMT1" t="inlineStr">
+      <c r="ANJ1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="AMU1" t="inlineStr">
+      <c r="ANK1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="AMV1" t="inlineStr">
+      <c r="ANL1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="AMW1" t="inlineStr">
+      <c r="ANM1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="AMX1" t="inlineStr">
+      <c r="ANN1" t="inlineStr">
         <is>
           <t>labels</t>
         </is>
       </c>
-      <c r="AMY1" t="inlineStr">
+      <c r="ANO1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="AMZ1" t="inlineStr">
+      <c r="ANP1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="ANA1" t="inlineStr">
+      <c r="ANQ1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="ANB1" t="inlineStr">
+      <c r="ANR1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="ANC1" t="inlineStr">
+      <c r="ANS1" t="inlineStr">
         <is>
           <t>occupation</t>
         </is>
       </c>
-      <c r="AND1" t="inlineStr">
+      <c r="ANT1" t="inlineStr">
         <is>
           <t>position</t>
         </is>
       </c>
-      <c r="ANE1" t="inlineStr">
+      <c r="ANU1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="ANF1" t="inlineStr">
+      <c r="ANV1" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="ANG1" t="inlineStr">
+      <c r="ANW1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="ANH1" t="inlineStr">
+      <c r="ANX1" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="ANI1" t="inlineStr">
+      <c r="ANY1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="ANJ1" t="inlineStr">
+      <c r="ANZ1" t="inlineStr">
         <is>
           <t>uri</t>
         </is>
       </c>
-      <c r="ANK1" t="inlineStr">
+      <c r="AOA1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="ANL1" t="inlineStr">
+      <c r="AOB1" t="inlineStr">
         <is>
           <t>links</t>
         </is>
       </c>
-      <c r="ANM1" t="inlineStr">
+      <c r="AOC1" t="inlineStr">
         <is>
           <t>href</t>
         </is>
       </c>
-      <c r="ANN1" t="inlineStr">
+      <c r="AOD1" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="ANO1" t="inlineStr">
+      <c r="AOE1" t="inlineStr">
         <is>
           <t>paths</t>
         </is>
       </c>
-      <c r="ANP1" t="inlineStr">
+      <c r="AOF1" t="inlineStr">
         <is>
           <t>permalink</t>
         </is>
       </c>
-      <c r="ANQ1" t="inlineStr">
+      <c r="AOG1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="ANR1" t="inlineStr">
+      <c r="AOH1" t="inlineStr">
         <is>
           <t>homepage</t>
         </is>
       </c>
-      <c r="ANS1" t="inlineStr">
+      <c r="AOI1" t="inlineStr">
         <is>
           <t>share</t>
         </is>

--- a/java/verify/fixtures/空列词表全量（ods_t_name_words）.xlsx
+++ b/java/verify/fixtures/空列词表全量（ods_t_name_words）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AOI1"/>
+  <dimension ref="A1:AOS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,3365 +2429,3415 @@
       </c>
       <c r="OM1" t="inlineStr">
         <is>
+          <t>发数</t>
+        </is>
+      </c>
+      <c r="ON1" t="inlineStr">
+        <is>
+          <t>航次</t>
+        </is>
+      </c>
+      <c r="OO1" t="inlineStr">
+        <is>
           <t>长度</t>
         </is>
       </c>
-      <c r="ON1" t="inlineStr">
+      <c r="OP1" t="inlineStr">
         <is>
           <t>宽度</t>
         </is>
       </c>
-      <c r="OO1" t="inlineStr">
+      <c r="OQ1" t="inlineStr">
         <is>
           <t>高度</t>
         </is>
       </c>
-      <c r="OP1" t="inlineStr">
+      <c r="OR1" t="inlineStr">
         <is>
           <t>厚度</t>
         </is>
       </c>
-      <c r="OQ1" t="inlineStr">
+      <c r="OS1" t="inlineStr">
         <is>
           <t>深度</t>
         </is>
       </c>
-      <c r="OR1" t="inlineStr">
+      <c r="OT1" t="inlineStr">
         <is>
           <t>距离</t>
         </is>
       </c>
-      <c r="OS1" t="inlineStr">
+      <c r="OU1" t="inlineStr">
         <is>
           <t>里程</t>
         </is>
       </c>
-      <c r="OT1" t="inlineStr">
+      <c r="OV1" t="inlineStr">
         <is>
           <t>面积</t>
         </is>
       </c>
-      <c r="OU1" t="inlineStr">
+      <c r="OW1" t="inlineStr">
         <is>
           <t>体积</t>
         </is>
       </c>
-      <c r="OV1" t="inlineStr">
+      <c r="OX1" t="inlineStr">
         <is>
           <t>容积</t>
         </is>
       </c>
-      <c r="OW1" t="inlineStr">
+      <c r="OY1" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="OX1" t="inlineStr">
+      <c r="OZ1" t="inlineStr">
         <is>
           <t>毛重</t>
         </is>
       </c>
-      <c r="OY1" t="inlineStr">
+      <c r="PA1" t="inlineStr">
         <is>
           <t>净重</t>
         </is>
       </c>
-      <c r="OZ1" t="inlineStr">
+      <c r="PB1" t="inlineStr">
         <is>
           <t>体重</t>
         </is>
       </c>
-      <c r="PA1" t="inlineStr">
+      <c r="PC1" t="inlineStr">
         <is>
           <t>载重</t>
         </is>
       </c>
-      <c r="PB1" t="inlineStr">
+      <c r="PD1" t="inlineStr">
         <is>
           <t>容量</t>
         </is>
       </c>
-      <c r="PC1" t="inlineStr">
+      <c r="PE1" t="inlineStr">
         <is>
           <t>温度</t>
         </is>
       </c>
-      <c r="PD1" t="inlineStr">
+      <c r="PF1" t="inlineStr">
         <is>
           <t>湿度</t>
         </is>
       </c>
-      <c r="PE1" t="inlineStr">
+      <c r="PG1" t="inlineStr">
         <is>
           <t>浓度</t>
         </is>
       </c>
-      <c r="PF1" t="inlineStr">
+      <c r="PH1" t="inlineStr">
         <is>
           <t>密度</t>
         </is>
       </c>
-      <c r="PG1" t="inlineStr">
+      <c r="PI1" t="inlineStr">
         <is>
           <t>压力</t>
         </is>
       </c>
-      <c r="PH1" t="inlineStr">
+      <c r="PJ1" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
-      <c r="PI1" t="inlineStr">
+      <c r="PK1" t="inlineStr">
         <is>
           <t>速率</t>
         </is>
       </c>
-      <c r="PJ1" t="inlineStr">
+      <c r="PL1" t="inlineStr">
         <is>
           <t>流量</t>
         </is>
       </c>
-      <c r="PK1" t="inlineStr">
+      <c r="PM1" t="inlineStr">
         <is>
           <t>电量</t>
         </is>
       </c>
-      <c r="PL1" t="inlineStr">
+      <c r="PN1" t="inlineStr">
         <is>
           <t>水量</t>
         </is>
       </c>
-      <c r="PM1" t="inlineStr">
+      <c r="PO1" t="inlineStr">
         <is>
           <t>气量</t>
         </is>
       </c>
-      <c r="PN1" t="inlineStr">
+      <c r="PP1" t="inlineStr">
         <is>
           <t>热量</t>
         </is>
       </c>
-      <c r="PO1" t="inlineStr">
+      <c r="PQ1" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
-      <c r="PP1" t="inlineStr">
+      <c r="PR1" t="inlineStr">
         <is>
           <t>电压</t>
         </is>
       </c>
-      <c r="PQ1" t="inlineStr">
+      <c r="PS1" t="inlineStr">
         <is>
           <t>电流</t>
         </is>
       </c>
-      <c r="PR1" t="inlineStr">
+      <c r="PT1" t="inlineStr">
         <is>
           <t>频率</t>
         </is>
       </c>
-      <c r="PS1" t="inlineStr">
+      <c r="PU1" t="inlineStr">
         <is>
           <t>海拔</t>
         </is>
       </c>
-      <c r="PT1" t="inlineStr">
+      <c r="PV1" t="inlineStr">
         <is>
           <t>高程</t>
         </is>
       </c>
-      <c r="PU1" t="inlineStr">
+      <c r="PW1" t="inlineStr">
         <is>
           <t>水位</t>
         </is>
       </c>
-      <c r="PV1" t="inlineStr">
+      <c r="PX1" t="inlineStr">
         <is>
           <t>雨量</t>
         </is>
       </c>
-      <c r="PW1" t="inlineStr">
+      <c r="PY1" t="inlineStr">
         <is>
           <t>身高</t>
         </is>
       </c>
-      <c r="PX1" t="inlineStr">
+      <c r="PZ1" t="inlineStr">
         <is>
           <t>含量</t>
         </is>
       </c>
-      <c r="PY1" t="inlineStr">
+      <c r="QA1" t="inlineStr">
         <is>
           <t>纯度</t>
         </is>
       </c>
-      <c r="PZ1" t="inlineStr">
+      <c r="QB1" t="inlineStr">
         <is>
           <t>直径</t>
         </is>
       </c>
-      <c r="QA1" t="inlineStr">
+      <c r="QC1" t="inlineStr">
         <is>
           <t>半径</t>
         </is>
       </c>
-      <c r="QB1" t="inlineStr">
+      <c r="QD1" t="inlineStr">
         <is>
           <t>周长</t>
         </is>
       </c>
-      <c r="QC1" t="inlineStr">
+      <c r="QE1" t="inlineStr">
         <is>
           <t>角度</t>
         </is>
       </c>
-      <c r="QD1" t="inlineStr">
+      <c r="QF1" t="inlineStr">
         <is>
           <t>间距</t>
         </is>
       </c>
-      <c r="QE1" t="inlineStr">
+      <c r="QG1" t="inlineStr">
         <is>
           <t>跨度</t>
         </is>
       </c>
-      <c r="QF1" t="inlineStr">
+      <c r="QH1" t="inlineStr">
         <is>
           <t>坡度</t>
         </is>
       </c>
-      <c r="QG1" t="inlineStr">
+      <c r="QI1" t="inlineStr">
         <is>
           <t>倾斜度</t>
         </is>
       </c>
-      <c r="QH1" t="inlineStr">
+      <c r="QJ1" t="inlineStr">
         <is>
           <t>粗糙度</t>
         </is>
       </c>
-      <c r="QI1" t="inlineStr">
+      <c r="QK1" t="inlineStr">
         <is>
           <t>平整度</t>
         </is>
       </c>
-      <c r="QJ1" t="inlineStr">
+      <c r="QL1" t="inlineStr">
         <is>
           <t>压实度</t>
         </is>
       </c>
-      <c r="QK1" t="inlineStr">
+      <c r="QM1" t="inlineStr">
         <is>
           <t>稠度</t>
         </is>
       </c>
-      <c r="QL1" t="inlineStr">
+      <c r="QN1" t="inlineStr">
         <is>
           <t>黏度</t>
         </is>
       </c>
-      <c r="QM1" t="inlineStr">
+      <c r="QO1" t="inlineStr">
         <is>
           <t>粘度</t>
         </is>
       </c>
-      <c r="QN1" t="inlineStr">
+      <c r="QP1" t="inlineStr">
         <is>
           <t>硬度</t>
         </is>
       </c>
-      <c r="QO1" t="inlineStr">
+      <c r="QQ1" t="inlineStr">
         <is>
           <t>强度</t>
         </is>
       </c>
-      <c r="QP1" t="inlineStr">
+      <c r="QR1" t="inlineStr">
         <is>
           <t>应力</t>
         </is>
       </c>
-      <c r="QQ1" t="inlineStr">
+      <c r="QS1" t="inlineStr">
         <is>
           <t>应变</t>
         </is>
       </c>
-      <c r="QR1" t="inlineStr">
+      <c r="QT1" t="inlineStr">
         <is>
           <t>模量</t>
         </is>
       </c>
-      <c r="QS1" t="inlineStr">
+      <c r="QU1" t="inlineStr">
         <is>
           <t>电阻</t>
         </is>
       </c>
-      <c r="QT1" t="inlineStr">
+      <c r="QV1" t="inlineStr">
         <is>
           <t>电容</t>
         </is>
       </c>
-      <c r="QU1" t="inlineStr">
+      <c r="QW1" t="inlineStr">
         <is>
           <t>电感</t>
         </is>
       </c>
-      <c r="QV1" t="inlineStr">
+      <c r="QX1" t="inlineStr">
         <is>
           <t>阻抗</t>
         </is>
       </c>
-      <c r="QW1" t="inlineStr">
+      <c r="QY1" t="inlineStr">
         <is>
           <t>能耗</t>
         </is>
       </c>
-      <c r="QX1" t="inlineStr">
+      <c r="QZ1" t="inlineStr">
         <is>
           <t>电耗</t>
         </is>
       </c>
-      <c r="QY1" t="inlineStr">
+      <c r="RA1" t="inlineStr">
         <is>
           <t>水耗</t>
         </is>
       </c>
-      <c r="QZ1" t="inlineStr">
+      <c r="RB1" t="inlineStr">
         <is>
           <t>热耗</t>
         </is>
       </c>
-      <c r="RA1" t="inlineStr">
+      <c r="RC1" t="inlineStr">
         <is>
           <t>油耗</t>
         </is>
       </c>
-      <c r="RB1" t="inlineStr">
+      <c r="RD1" t="inlineStr">
         <is>
           <t>气耗</t>
         </is>
       </c>
-      <c r="RC1" t="inlineStr">
+      <c r="RE1" t="inlineStr">
         <is>
           <t>煤耗</t>
         </is>
       </c>
-      <c r="RD1" t="inlineStr">
+      <c r="RF1" t="inlineStr">
         <is>
           <t>产能</t>
         </is>
       </c>
-      <c r="RE1" t="inlineStr">
+      <c r="RG1" t="inlineStr">
         <is>
           <t>吨位</t>
         </is>
       </c>
-      <c r="RF1" t="inlineStr">
+      <c r="RH1" t="inlineStr">
         <is>
           <t>载荷</t>
         </is>
       </c>
-      <c r="RG1" t="inlineStr">
+      <c r="RI1" t="inlineStr">
         <is>
           <t>荷载</t>
         </is>
       </c>
-      <c r="RH1" t="inlineStr">
+      <c r="RJ1" t="inlineStr">
         <is>
           <t>压强</t>
         </is>
       </c>
-      <c r="RI1" t="inlineStr">
+      <c r="RK1" t="inlineStr">
         <is>
           <t>液压</t>
         </is>
       </c>
-      <c r="RJ1" t="inlineStr">
+      <c r="RL1" t="inlineStr">
         <is>
           <t>气压</t>
         </is>
       </c>
-      <c r="RK1" t="inlineStr">
+      <c r="RM1" t="inlineStr">
         <is>
           <t>风速</t>
         </is>
       </c>
-      <c r="RL1" t="inlineStr">
+      <c r="RN1" t="inlineStr">
         <is>
           <t>流速</t>
         </is>
       </c>
-      <c r="RM1" t="inlineStr">
+      <c r="RO1" t="inlineStr">
         <is>
           <t>照度</t>
         </is>
       </c>
-      <c r="RN1" t="inlineStr">
+      <c r="RP1" t="inlineStr">
         <is>
           <t>亮度</t>
         </is>
       </c>
-      <c r="RO1" t="inlineStr">
+      <c r="RQ1" t="inlineStr">
         <is>
           <t>色度</t>
         </is>
       </c>
-      <c r="RP1" t="inlineStr">
+      <c r="RR1" t="inlineStr">
         <is>
           <t>浊度</t>
         </is>
       </c>
-      <c r="RQ1" t="inlineStr">
+      <c r="RS1" t="inlineStr">
         <is>
           <t>盐度</t>
         </is>
       </c>
-      <c r="RR1" t="inlineStr">
+      <c r="RT1" t="inlineStr">
         <is>
           <t>酸度</t>
         </is>
       </c>
-      <c r="RS1" t="inlineStr">
+      <c r="RU1" t="inlineStr">
         <is>
           <t>碱度</t>
         </is>
       </c>
-      <c r="RT1" t="inlineStr">
+      <c r="RV1" t="inlineStr">
         <is>
           <t>温差</t>
         </is>
       </c>
-      <c r="RU1" t="inlineStr">
+      <c r="RW1" t="inlineStr">
         <is>
           <t>体温</t>
         </is>
       </c>
-      <c r="RV1" t="inlineStr">
+      <c r="RX1" t="inlineStr">
         <is>
           <t>扬程</t>
         </is>
       </c>
-      <c r="RW1" t="inlineStr">
+      <c r="RY1" t="inlineStr">
         <is>
           <t>库容</t>
         </is>
       </c>
-      <c r="RX1" t="inlineStr">
+      <c r="RZ1" t="inlineStr">
         <is>
           <t>含沙量</t>
         </is>
       </c>
-      <c r="RY1" t="inlineStr">
+      <c r="SA1" t="inlineStr">
         <is>
           <t>溶解氧</t>
         </is>
       </c>
-      <c r="RZ1" t="inlineStr">
+      <c r="SB1" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="SA1" t="inlineStr">
+      <c r="SC1" t="inlineStr">
         <is>
           <t>断面</t>
         </is>
       </c>
-      <c r="SB1" t="inlineStr">
+      <c r="SD1" t="inlineStr">
         <is>
           <t>管径</t>
         </is>
       </c>
-      <c r="SC1" t="inlineStr">
+      <c r="SE1" t="inlineStr">
         <is>
           <t>线径</t>
         </is>
       </c>
-      <c r="SD1" t="inlineStr">
+      <c r="SF1" t="inlineStr">
         <is>
           <t>粒径</t>
         </is>
       </c>
-      <c r="SE1" t="inlineStr">
+      <c r="SG1" t="inlineStr">
         <is>
           <t>粒度</t>
         </is>
       </c>
-      <c r="SF1" t="inlineStr">
+      <c r="SH1" t="inlineStr">
         <is>
           <t>负荷</t>
         </is>
       </c>
-      <c r="SG1" t="inlineStr">
+      <c r="SI1" t="inlineStr">
         <is>
           <t>壁厚</t>
         </is>
       </c>
-      <c r="SH1" t="inlineStr">
+      <c r="SJ1" t="inlineStr">
         <is>
           <t>净高</t>
         </is>
       </c>
-      <c r="SI1" t="inlineStr">
+      <c r="SK1" t="inlineStr">
         <is>
           <t>净空</t>
         </is>
       </c>
-      <c r="SJ1" t="inlineStr">
+      <c r="SL1" t="inlineStr">
         <is>
           <t>埋深</t>
         </is>
       </c>
-      <c r="SK1" t="inlineStr">
+      <c r="SM1" t="inlineStr">
         <is>
           <t>覆土</t>
         </is>
       </c>
-      <c r="SL1" t="inlineStr">
+      <c r="SN1" t="inlineStr">
         <is>
           <t>进深</t>
         </is>
       </c>
-      <c r="SM1" t="inlineStr">
+      <c r="SO1" t="inlineStr">
         <is>
           <t>开间</t>
         </is>
       </c>
-      <c r="SN1" t="inlineStr">
+      <c r="SP1" t="inlineStr">
         <is>
           <t>视距</t>
         </is>
       </c>
-      <c r="SO1" t="inlineStr">
+      <c r="SQ1" t="inlineStr">
         <is>
           <t>弧长</t>
         </is>
       </c>
-      <c r="SP1" t="inlineStr">
+      <c r="SR1" t="inlineStr">
         <is>
           <t>弦长</t>
         </is>
       </c>
-      <c r="SQ1" t="inlineStr">
+      <c r="SS1" t="inlineStr">
         <is>
           <t>振幅</t>
         </is>
       </c>
-      <c r="SR1" t="inlineStr">
+      <c r="ST1" t="inlineStr">
         <is>
           <t>挠度</t>
         </is>
       </c>
-      <c r="SS1" t="inlineStr">
+      <c r="SU1" t="inlineStr">
         <is>
           <t>沉降</t>
         </is>
       </c>
-      <c r="ST1" t="inlineStr">
+      <c r="SV1" t="inlineStr">
         <is>
           <t>位移</t>
         </is>
       </c>
-      <c r="SU1" t="inlineStr">
+      <c r="SW1" t="inlineStr">
         <is>
           <t>变形量</t>
         </is>
       </c>
-      <c r="SV1" t="inlineStr">
+      <c r="SX1" t="inlineStr">
         <is>
           <t>噪声</t>
         </is>
       </c>
-      <c r="SW1" t="inlineStr">
+      <c r="SY1" t="inlineStr">
         <is>
           <t>噪音</t>
         </is>
       </c>
-      <c r="SX1" t="inlineStr">
+      <c r="SZ1" t="inlineStr">
         <is>
           <t>分贝</t>
         </is>
       </c>
-      <c r="SY1" t="inlineStr">
+      <c r="TA1" t="inlineStr">
         <is>
           <t>辐射</t>
         </is>
       </c>
-      <c r="SZ1" t="inlineStr">
+      <c r="TB1" t="inlineStr">
         <is>
           <t>总磷</t>
         </is>
       </c>
-      <c r="TA1" t="inlineStr">
+      <c r="TC1" t="inlineStr">
         <is>
           <t>总氮</t>
         </is>
       </c>
-      <c r="TB1" t="inlineStr">
+      <c r="TD1" t="inlineStr">
         <is>
           <t>含水</t>
         </is>
       </c>
-      <c r="TC1" t="inlineStr">
+      <c r="TE1" t="inlineStr">
         <is>
           <t>航程</t>
         </is>
       </c>
-      <c r="TD1" t="inlineStr">
+      <c r="TF1" t="inlineStr">
         <is>
           <t>航速</t>
         </is>
       </c>
-      <c r="TE1" t="inlineStr">
+      <c r="TG1" t="inlineStr">
         <is>
           <t>转速</t>
         </is>
       </c>
-      <c r="TF1" t="inlineStr">
+      <c r="TH1" t="inlineStr">
         <is>
           <t>亩产</t>
         </is>
       </c>
-      <c r="TG1" t="inlineStr">
+      <c r="TI1" t="inlineStr">
         <is>
           <t>血糖</t>
         </is>
       </c>
-      <c r="TH1" t="inlineStr">
+      <c r="TJ1" t="inlineStr">
         <is>
           <t>视力</t>
         </is>
       </c>
-      <c r="TI1" t="inlineStr">
+      <c r="TK1" t="inlineStr">
         <is>
           <t>剂量</t>
         </is>
       </c>
-      <c r="TJ1" t="inlineStr">
+      <c r="TL1" t="inlineStr">
         <is>
           <t>用药量</t>
         </is>
       </c>
-      <c r="TK1" t="inlineStr">
+      <c r="TM1" t="inlineStr">
+        <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="TN1" t="inlineStr">
+        <is>
+          <t>射高</t>
+        </is>
+      </c>
+      <c r="TO1" t="inlineStr">
+        <is>
+          <t>射速</t>
+        </is>
+      </c>
+      <c r="TP1" t="inlineStr">
+        <is>
+          <t>仰角</t>
+        </is>
+      </c>
+      <c r="TQ1" t="inlineStr">
+        <is>
+          <t>炮径</t>
+        </is>
+      </c>
+      <c r="TR1" t="inlineStr">
+        <is>
+          <t>弹径</t>
+        </is>
+      </c>
+      <c r="TS1" t="inlineStr">
+        <is>
+          <t>装药量</t>
+        </is>
+      </c>
+      <c r="TT1" t="inlineStr">
+        <is>
+          <t>自重</t>
+        </is>
+      </c>
+      <c r="TU1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="TL1" t="inlineStr">
+      <c r="TV1" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="TM1" t="inlineStr">
+      <c r="TW1" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="TN1" t="inlineStr">
+      <c r="TX1" t="inlineStr">
         <is>
           <t>名次</t>
         </is>
       </c>
-      <c r="TO1" t="inlineStr">
+      <c r="TY1" t="inlineStr">
         <is>
           <t>页码</t>
         </is>
       </c>
-      <c r="TP1" t="inlineStr">
+      <c r="TZ1" t="inlineStr">
         <is>
           <t>页数</t>
         </is>
       </c>
-      <c r="TQ1" t="inlineStr">
+      <c r="UA1" t="inlineStr">
         <is>
           <t>层数</t>
         </is>
       </c>
-      <c r="TR1" t="inlineStr">
+      <c r="UB1" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="TS1" t="inlineStr">
+      <c r="UC1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="TT1" t="inlineStr">
+      <c r="UD1" t="inlineStr">
         <is>
           <t>位次</t>
         </is>
       </c>
-      <c r="TU1" t="inlineStr">
+      <c r="UE1" t="inlineStr">
         <is>
           <t>座次</t>
         </is>
       </c>
-      <c r="TV1" t="inlineStr">
+      <c r="UF1" t="inlineStr">
         <is>
           <t>位序</t>
         </is>
       </c>
-      <c r="TW1" t="inlineStr">
+      <c r="UG1" t="inlineStr">
         <is>
           <t>顺位</t>
         </is>
       </c>
-      <c r="TX1" t="inlineStr">
+      <c r="UH1" t="inlineStr">
         <is>
           <t>序位</t>
         </is>
       </c>
-      <c r="TY1" t="inlineStr">
+      <c r="UI1" t="inlineStr">
         <is>
           <t>比例</t>
         </is>
       </c>
-      <c r="TZ1" t="inlineStr">
+      <c r="UJ1" t="inlineStr">
         <is>
           <t>百分比</t>
         </is>
       </c>
-      <c r="UA1" t="inlineStr">
+      <c r="UK1" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
-      <c r="UB1" t="inlineStr">
+      <c r="UL1" t="inlineStr">
         <is>
           <t>增速</t>
         </is>
       </c>
-      <c r="UC1" t="inlineStr">
+      <c r="UM1" t="inlineStr">
         <is>
           <t>幅度</t>
         </is>
       </c>
-      <c r="UD1" t="inlineStr">
+      <c r="UN1" t="inlineStr">
         <is>
           <t>系数</t>
         </is>
       </c>
-      <c r="UE1" t="inlineStr">
+      <c r="UO1" t="inlineStr">
         <is>
           <t>因数</t>
         </is>
       </c>
-      <c r="UF1" t="inlineStr">
+      <c r="UP1" t="inlineStr">
         <is>
           <t>倍数</t>
         </is>
       </c>
-      <c r="UG1" t="inlineStr">
+      <c r="UQ1" t="inlineStr">
         <is>
           <t>折扣</t>
         </is>
       </c>
-      <c r="UH1" t="inlineStr">
+      <c r="UR1" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="UI1" t="inlineStr">
+      <c r="US1" t="inlineStr">
         <is>
           <t>比重</t>
         </is>
       </c>
-      <c r="UJ1" t="inlineStr">
+      <c r="UT1" t="inlineStr">
         <is>
           <t>容积率</t>
         </is>
       </c>
-      <c r="UK1" t="inlineStr">
+      <c r="UU1" t="inlineStr">
         <is>
           <t>概率</t>
         </is>
       </c>
-      <c r="UL1" t="inlineStr">
+      <c r="UV1" t="inlineStr">
         <is>
           <t>比值</t>
         </is>
       </c>
-      <c r="UM1" t="inlineStr">
+      <c r="UW1" t="inlineStr">
         <is>
           <t>份额</t>
         </is>
       </c>
-      <c r="UN1" t="inlineStr">
+      <c r="UX1" t="inlineStr">
         <is>
           <t>百分点</t>
         </is>
       </c>
-      <c r="UO1" t="inlineStr">
+      <c r="UY1" t="inlineStr">
         <is>
           <t>配比</t>
         </is>
       </c>
-      <c r="UP1" t="inlineStr">
+      <c r="UZ1" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
       </c>
-      <c r="UQ1" t="inlineStr">
+      <c r="VA1" t="inlineStr">
         <is>
           <t>评分</t>
         </is>
       </c>
-      <c r="UR1" t="inlineStr">
+      <c r="VB1" t="inlineStr">
         <is>
           <t>分数</t>
         </is>
       </c>
-      <c r="US1" t="inlineStr">
+      <c r="VC1" t="inlineStr">
         <is>
           <t>成绩</t>
         </is>
       </c>
-      <c r="UT1" t="inlineStr">
+      <c r="VD1" t="inlineStr">
         <is>
           <t>总分</t>
         </is>
       </c>
-      <c r="UU1" t="inlineStr">
+      <c r="VE1" t="inlineStr">
         <is>
           <t>平均分</t>
         </is>
       </c>
-      <c r="UV1" t="inlineStr">
+      <c r="VF1" t="inlineStr">
         <is>
           <t>绩点</t>
         </is>
       </c>
-      <c r="UW1" t="inlineStr">
+      <c r="VG1" t="inlineStr">
         <is>
           <t>分值</t>
         </is>
       </c>
-      <c r="UX1" t="inlineStr">
+      <c r="VH1" t="inlineStr">
         <is>
           <t>满意度</t>
         </is>
       </c>
-      <c r="UY1" t="inlineStr">
+      <c r="VI1" t="inlineStr">
         <is>
           <t>星级</t>
         </is>
       </c>
-      <c r="UZ1" t="inlineStr">
+      <c r="VJ1" t="inlineStr">
         <is>
           <t>扣分</t>
         </is>
       </c>
-      <c r="VA1" t="inlineStr">
+      <c r="VK1" t="inlineStr">
         <is>
           <t>加分</t>
         </is>
       </c>
-      <c r="VB1" t="inlineStr">
+      <c r="VL1" t="inlineStr">
         <is>
           <t>基准分</t>
         </is>
       </c>
-      <c r="VC1" t="inlineStr">
+      <c r="VM1" t="inlineStr">
         <is>
           <t>考核分</t>
         </is>
       </c>
-      <c r="VD1" t="inlineStr">
+      <c r="VN1" t="inlineStr">
         <is>
           <t>理论分</t>
         </is>
       </c>
-      <c r="VE1" t="inlineStr">
+      <c r="VO1" t="inlineStr">
         <is>
           <t>实操分</t>
         </is>
       </c>
-      <c r="VF1" t="inlineStr">
+      <c r="VP1" t="inlineStr">
         <is>
           <t>体能分</t>
         </is>
       </c>
-      <c r="VG1" t="inlineStr">
+      <c r="VQ1" t="inlineStr">
         <is>
           <t>技能分</t>
         </is>
       </c>
-      <c r="VH1" t="inlineStr">
+      <c r="VR1" t="inlineStr">
         <is>
           <t>综合分</t>
         </is>
       </c>
-      <c r="VI1" t="inlineStr">
+      <c r="VS1" t="inlineStr">
         <is>
           <t>总评</t>
         </is>
       </c>
-      <c r="VJ1" t="inlineStr">
+      <c r="VT1" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="VK1" t="inlineStr">
+      <c r="VU1" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="VL1" t="inlineStr">
+      <c r="VV1" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="VM1" t="inlineStr">
+      <c r="VW1" t="inlineStr">
         <is>
           <t>共计</t>
         </is>
       </c>
-      <c r="VN1" t="inlineStr">
+      <c r="VX1" t="inlineStr">
         <is>
           <t>累计</t>
         </is>
       </c>
-      <c r="VO1" t="inlineStr">
+      <c r="VY1" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="VP1" t="inlineStr">
+      <c r="VZ1" t="inlineStr">
         <is>
           <t>总量</t>
         </is>
       </c>
-      <c r="VQ1" t="inlineStr">
+      <c r="WA1" t="inlineStr">
         <is>
           <t>总值</t>
         </is>
       </c>
-      <c r="VR1" t="inlineStr">
+      <c r="WB1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="VS1" t="inlineStr">
+      <c r="WC1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="VT1" t="inlineStr">
+      <c r="WD1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="VU1" t="inlineStr">
+      <c r="WE1" t="inlineStr">
         <is>
           <t>详情</t>
         </is>
       </c>
-      <c r="VV1" t="inlineStr">
+      <c r="WF1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="VW1" t="inlineStr">
+      <c r="WG1" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="VX1" t="inlineStr">
+      <c r="WH1" t="inlineStr">
         <is>
           <t>简介</t>
         </is>
       </c>
-      <c r="VY1" t="inlineStr">
+      <c r="WI1" t="inlineStr">
         <is>
           <t>评价</t>
         </is>
       </c>
-      <c r="VZ1" t="inlineStr">
+      <c r="WJ1" t="inlineStr">
         <is>
           <t>意见</t>
         </is>
       </c>
-      <c r="WA1" t="inlineStr">
+      <c r="WK1" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="WB1" t="inlineStr">
+      <c r="WL1" t="inlineStr">
         <is>
           <t>要求</t>
         </is>
       </c>
-      <c r="WC1" t="inlineStr">
+      <c r="WM1" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
       </c>
-      <c r="WD1" t="inlineStr">
+      <c r="WN1" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="WE1" t="inlineStr">
+      <c r="WO1" t="inlineStr">
         <is>
           <t>经过</t>
         </is>
       </c>
-      <c r="WF1" t="inlineStr">
+      <c r="WP1" t="inlineStr">
         <is>
           <t>措施</t>
         </is>
       </c>
-      <c r="WG1" t="inlineStr">
+      <c r="WQ1" t="inlineStr">
         <is>
           <t>职责</t>
         </is>
       </c>
-      <c r="WH1" t="inlineStr">
+      <c r="WR1" t="inlineStr">
         <is>
           <t>业绩</t>
         </is>
       </c>
-      <c r="WI1" t="inlineStr">
+      <c r="WS1" t="inlineStr">
         <is>
           <t>事迹</t>
         </is>
       </c>
-      <c r="WJ1" t="inlineStr">
+      <c r="WT1" t="inlineStr">
         <is>
           <t>案情</t>
         </is>
       </c>
-      <c r="WK1" t="inlineStr">
+      <c r="WU1" t="inlineStr">
         <is>
           <t>附注</t>
         </is>
       </c>
-      <c r="WL1" t="inlineStr">
+      <c r="WV1" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="WM1" t="inlineStr">
+      <c r="WW1" t="inlineStr">
         <is>
           <t>正文</t>
         </is>
       </c>
-      <c r="WN1" t="inlineStr">
+      <c r="WX1" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="WO1" t="inlineStr">
+      <c r="WY1" t="inlineStr">
         <is>
           <t>结论</t>
         </is>
       </c>
-      <c r="WP1" t="inlineStr">
+      <c r="WZ1" t="inlineStr">
         <is>
           <t>经营范围</t>
         </is>
       </c>
-      <c r="WQ1" t="inlineStr">
+      <c r="XA1" t="inlineStr">
         <is>
           <t>注意事项</t>
         </is>
       </c>
-      <c r="WR1" t="inlineStr">
+      <c r="XB1" t="inlineStr">
         <is>
           <t>特点</t>
         </is>
       </c>
-      <c r="WS1" t="inlineStr">
+      <c r="XC1" t="inlineStr">
         <is>
           <t>优势</t>
         </is>
       </c>
-      <c r="WT1" t="inlineStr">
+      <c r="XD1" t="inlineStr">
         <is>
           <t>亮点</t>
         </is>
       </c>
-      <c r="WU1" t="inlineStr">
+      <c r="XE1" t="inlineStr">
         <is>
           <t>留言</t>
         </is>
       </c>
-      <c r="WV1" t="inlineStr">
+      <c r="XF1" t="inlineStr">
         <is>
           <t>反馈</t>
         </is>
       </c>
-      <c r="WW1" t="inlineStr">
+      <c r="XG1" t="inlineStr">
         <is>
           <t>答复</t>
         </is>
       </c>
-      <c r="WX1" t="inlineStr">
+      <c r="XH1" t="inlineStr">
         <is>
           <t>回复</t>
         </is>
       </c>
-      <c r="WY1" t="inlineStr">
+      <c r="XI1" t="inlineStr">
         <is>
           <t>心得</t>
         </is>
       </c>
-      <c r="WZ1" t="inlineStr">
+      <c r="XJ1" t="inlineStr">
         <is>
           <t>体会</t>
         </is>
       </c>
-      <c r="XA1" t="inlineStr">
+      <c r="XK1" t="inlineStr">
         <is>
           <t>感想</t>
         </is>
       </c>
-      <c r="XB1" t="inlineStr">
+      <c r="XL1" t="inlineStr">
         <is>
           <t>承诺</t>
         </is>
       </c>
-      <c r="XC1" t="inlineStr">
+      <c r="XM1" t="inlineStr">
         <is>
           <t>条款</t>
         </is>
       </c>
-      <c r="XD1" t="inlineStr">
+      <c r="XN1" t="inlineStr">
         <is>
           <t>批注</t>
         </is>
       </c>
-      <c r="XE1" t="inlineStr">
+      <c r="XO1" t="inlineStr">
         <is>
           <t>点评</t>
         </is>
       </c>
-      <c r="XF1" t="inlineStr">
+      <c r="XP1" t="inlineStr">
         <is>
           <t>陈述</t>
         </is>
       </c>
-      <c r="XG1" t="inlineStr">
+      <c r="XQ1" t="inlineStr">
         <is>
           <t>供述</t>
         </is>
       </c>
-      <c r="XH1" t="inlineStr">
+      <c r="XR1" t="inlineStr">
         <is>
           <t>证言</t>
         </is>
       </c>
-      <c r="XI1" t="inlineStr">
+      <c r="XS1" t="inlineStr">
         <is>
           <t>笔录</t>
         </is>
       </c>
-      <c r="XJ1" t="inlineStr">
+      <c r="XT1" t="inlineStr">
         <is>
           <t>诉求</t>
         </is>
       </c>
-      <c r="XK1" t="inlineStr">
+      <c r="XU1" t="inlineStr">
         <is>
           <t>主张</t>
         </is>
       </c>
-      <c r="XL1" t="inlineStr">
+      <c r="XV1" t="inlineStr">
         <is>
           <t>情况</t>
         </is>
       </c>
-      <c r="XM1" t="inlineStr">
+      <c r="XW1" t="inlineStr">
         <is>
           <t>事由</t>
         </is>
       </c>
-      <c r="XN1" t="inlineStr">
+      <c r="XX1" t="inlineStr">
         <is>
           <t>纪要</t>
         </is>
       </c>
-      <c r="XO1" t="inlineStr">
+      <c r="XY1" t="inlineStr">
         <is>
           <t>做法</t>
         </is>
       </c>
-      <c r="XP1" t="inlineStr">
+      <c r="XZ1" t="inlineStr">
         <is>
           <t>成效</t>
         </is>
       </c>
-      <c r="XQ1" t="inlineStr">
+      <c r="YA1" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="XR1" t="inlineStr">
+      <c r="YB1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="XS1" t="inlineStr">
+      <c r="YC1" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="XT1" t="inlineStr">
+      <c r="YD1" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="XU1" t="inlineStr">
+      <c r="YE1" t="inlineStr">
         <is>
           <t>题目</t>
         </is>
       </c>
-      <c r="XV1" t="inlineStr">
+      <c r="YF1" t="inlineStr">
         <is>
           <t>主题</t>
         </is>
       </c>
-      <c r="XW1" t="inlineStr">
+      <c r="YG1" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="XX1" t="inlineStr">
+      <c r="YH1" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="XY1" t="inlineStr">
+      <c r="YI1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="XZ1" t="inlineStr">
+      <c r="YJ1" t="inlineStr">
         <is>
           <t>种类</t>
         </is>
       </c>
-      <c r="YA1" t="inlineStr">
+      <c r="YK1" t="inlineStr">
         <is>
           <t>品种</t>
         </is>
       </c>
-      <c r="YB1" t="inlineStr">
+      <c r="YL1" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="YC1" t="inlineStr">
+      <c r="YM1" t="inlineStr">
         <is>
           <t>型号</t>
         </is>
       </c>
-      <c r="YD1" t="inlineStr">
+      <c r="YN1" t="inlineStr">
         <is>
           <t>规格</t>
         </is>
       </c>
-      <c r="YE1" t="inlineStr">
+      <c r="YO1" t="inlineStr">
         <is>
           <t>材质</t>
         </is>
       </c>
-      <c r="YF1" t="inlineStr">
+      <c r="YP1" t="inlineStr">
         <is>
           <t>颜色</t>
         </is>
       </c>
-      <c r="YG1" t="inlineStr">
+      <c r="YQ1" t="inlineStr">
         <is>
           <t>尺码</t>
         </is>
       </c>
-      <c r="YH1" t="inlineStr">
+      <c r="YR1" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="YI1" t="inlineStr">
+      <c r="YS1" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="YJ1" t="inlineStr">
+      <c r="YT1" t="inlineStr">
         <is>
           <t>机构</t>
         </is>
       </c>
-      <c r="YK1" t="inlineStr">
+      <c r="YU1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="YL1" t="inlineStr">
+      <c r="YV1" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="YM1" t="inlineStr">
+      <c r="YW1" t="inlineStr">
         <is>
           <t>组织</t>
         </is>
       </c>
-      <c r="YN1" t="inlineStr">
+      <c r="YX1" t="inlineStr">
         <is>
           <t>学校</t>
         </is>
       </c>
-      <c r="YO1" t="inlineStr">
+      <c r="YY1" t="inlineStr">
         <is>
           <t>医院</t>
         </is>
       </c>
-      <c r="YP1" t="inlineStr">
+      <c r="YZ1" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="YQ1" t="inlineStr">
+      <c r="ZA1" t="inlineStr">
         <is>
           <t>工程</t>
         </is>
       </c>
-      <c r="YR1" t="inlineStr">
+      <c r="ZB1" t="inlineStr">
         <is>
           <t>标段</t>
         </is>
       </c>
-      <c r="YS1" t="inlineStr">
+      <c r="ZC1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="YT1" t="inlineStr">
+      <c r="ZD1" t="inlineStr">
         <is>
           <t>渠道</t>
         </is>
       </c>
-      <c r="YU1" t="inlineStr">
+      <c r="ZE1" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="YV1" t="inlineStr">
+      <c r="ZF1" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="YW1" t="inlineStr">
+      <c r="ZG1" t="inlineStr">
         <is>
           <t>地址</t>
         </is>
       </c>
-      <c r="YX1" t="inlineStr">
+      <c r="ZH1" t="inlineStr">
         <is>
           <t>联系人</t>
         </is>
       </c>
-      <c r="YY1" t="inlineStr">
+      <c r="ZI1" t="inlineStr">
         <is>
           <t>职务</t>
         </is>
       </c>
-      <c r="YZ1" t="inlineStr">
+      <c r="ZJ1" t="inlineStr">
         <is>
           <t>职业</t>
         </is>
       </c>
-      <c r="ZA1" t="inlineStr">
+      <c r="ZK1" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="ZB1" t="inlineStr">
+      <c r="ZL1" t="inlineStr">
         <is>
           <t>课程</t>
         </is>
       </c>
-      <c r="ZC1" t="inlineStr">
+      <c r="ZM1" t="inlineStr">
         <is>
           <t>标准</t>
         </is>
       </c>
-      <c r="ZD1" t="inlineStr">
+      <c r="ZN1" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
-      <c r="ZE1" t="inlineStr">
+      <c r="ZO1" t="inlineStr">
         <is>
           <t>方式</t>
         </is>
       </c>
-      <c r="ZF1" t="inlineStr">
+      <c r="ZP1" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
       </c>
-      <c r="ZG1" t="inlineStr">
+      <c r="ZQ1" t="inlineStr">
         <is>
           <t>工艺</t>
         </is>
       </c>
-      <c r="ZH1" t="inlineStr">
+      <c r="ZR1" t="inlineStr">
         <is>
           <t>工序</t>
         </is>
       </c>
-      <c r="ZI1" t="inlineStr">
+      <c r="ZS1" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="ZJ1" t="inlineStr">
+      <c r="ZT1" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="ZK1" t="inlineStr">
+      <c r="ZU1" t="inlineStr">
         <is>
           <t>称谓</t>
         </is>
       </c>
-      <c r="ZL1" t="inlineStr">
+      <c r="ZV1" t="inlineStr">
         <is>
           <t>职称</t>
         </is>
       </c>
-      <c r="ZM1" t="inlineStr">
+      <c r="ZW1" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="ZN1" t="inlineStr">
+      <c r="ZX1" t="inlineStr">
         <is>
           <t>职位</t>
         </is>
       </c>
-      <c r="ZO1" t="inlineStr">
+      <c r="ZY1" t="inlineStr">
         <is>
           <t>科室</t>
         </is>
       </c>
-      <c r="ZP1" t="inlineStr">
+      <c r="ZZ1" t="inlineStr">
         <is>
           <t>班组</t>
         </is>
       </c>
-      <c r="ZQ1" t="inlineStr">
+      <c r="AAA1" t="inlineStr">
         <is>
           <t>班级</t>
         </is>
       </c>
-      <c r="ZR1" t="inlineStr">
+      <c r="AAB1" t="inlineStr">
         <is>
           <t>专业</t>
         </is>
       </c>
-      <c r="ZS1" t="inlineStr">
+      <c r="AAC1" t="inlineStr">
         <is>
           <t>院系</t>
         </is>
       </c>
-      <c r="ZT1" t="inlineStr">
+      <c r="AAD1" t="inlineStr">
         <is>
           <t>校区</t>
         </is>
       </c>
-      <c r="ZU1" t="inlineStr">
+      <c r="AAE1" t="inlineStr">
         <is>
           <t>场馆</t>
         </is>
       </c>
-      <c r="ZV1" t="inlineStr">
+      <c r="AAF1" t="inlineStr">
         <is>
           <t>楼盘</t>
         </is>
       </c>
-      <c r="ZW1" t="inlineStr">
+      <c r="AAG1" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="ZX1" t="inlineStr">
+      <c r="AAH1" t="inlineStr">
         <is>
           <t>街道</t>
         </is>
       </c>
-      <c r="ZY1" t="inlineStr">
+      <c r="AAI1" t="inlineStr">
         <is>
           <t>社区</t>
         </is>
       </c>
-      <c r="ZZ1" t="inlineStr">
+      <c r="AAJ1" t="inlineStr">
         <is>
           <t>村镇</t>
         </is>
       </c>
-      <c r="AAA1" t="inlineStr">
+      <c r="AAK1" t="inlineStr">
         <is>
           <t>路段</t>
         </is>
       </c>
-      <c r="AAB1" t="inlineStr">
+      <c r="AAL1" t="inlineStr">
         <is>
           <t>线路</t>
         </is>
       </c>
-      <c r="AAC1" t="inlineStr">
+      <c r="AAM1" t="inlineStr">
         <is>
           <t>管线</t>
         </is>
       </c>
-      <c r="AAD1" t="inlineStr">
+      <c r="AAN1" t="inlineStr">
         <is>
           <t>站点</t>
         </is>
       </c>
-      <c r="AAE1" t="inlineStr">
+      <c r="AAO1" t="inlineStr">
         <is>
           <t>品名</t>
         </is>
       </c>
-      <c r="AAF1" t="inlineStr">
+      <c r="AAP1" t="inlineStr">
         <is>
           <t>别名</t>
         </is>
       </c>
-      <c r="AAG1" t="inlineStr">
+      <c r="AAQ1" t="inlineStr">
         <is>
           <t>曾用名</t>
         </is>
       </c>
-      <c r="AAH1" t="inlineStr">
+      <c r="AAR1" t="inlineStr">
         <is>
           <t>简称</t>
         </is>
       </c>
-      <c r="AAI1" t="inlineStr">
+      <c r="AAS1" t="inlineStr">
         <is>
           <t>全称</t>
         </is>
       </c>
-      <c r="AAJ1" t="inlineStr">
+      <c r="AAT1" t="inlineStr">
         <is>
           <t>栏目</t>
         </is>
       </c>
-      <c r="AAK1" t="inlineStr">
+      <c r="AAU1" t="inlineStr">
         <is>
           <t>频道</t>
         </is>
       </c>
-      <c r="AAL1" t="inlineStr">
+      <c r="AAV1" t="inlineStr">
         <is>
           <t>语种</t>
         </is>
       </c>
-      <c r="AAM1" t="inlineStr">
+      <c r="AAW1" t="inlineStr">
         <is>
           <t>币种</t>
         </is>
       </c>
-      <c r="AAN1" t="inlineStr">
+      <c r="AAX1" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="AAO1" t="inlineStr">
+      <c r="AAY1" t="inlineStr">
         <is>
           <t>经办人</t>
         </is>
       </c>
-      <c r="AAP1" t="inlineStr">
+      <c r="AAZ1" t="inlineStr">
         <is>
           <t>审核人</t>
         </is>
       </c>
-      <c r="AAQ1" t="inlineStr">
+      <c r="ABA1" t="inlineStr">
         <is>
           <t>批准人</t>
         </is>
       </c>
-      <c r="AAR1" t="inlineStr">
+      <c r="ABB1" t="inlineStr">
         <is>
           <t>填报人</t>
         </is>
       </c>
-      <c r="AAS1" t="inlineStr">
+      <c r="ABC1" t="inlineStr">
         <is>
           <t>编制人</t>
         </is>
       </c>
-      <c r="AAT1" t="inlineStr">
+      <c r="ABD1" t="inlineStr">
         <is>
           <t>责任人</t>
         </is>
       </c>
-      <c r="AAU1" t="inlineStr">
+      <c r="ABE1" t="inlineStr">
         <is>
           <t>申请人</t>
         </is>
       </c>
-      <c r="AAV1" t="inlineStr">
+      <c r="ABF1" t="inlineStr">
         <is>
           <t>受理人</t>
         </is>
       </c>
-      <c r="AAW1" t="inlineStr">
+      <c r="ABG1" t="inlineStr">
         <is>
           <t>创建人</t>
         </is>
       </c>
-      <c r="AAX1" t="inlineStr">
+      <c r="ABH1" t="inlineStr">
         <is>
           <t>修改人</t>
         </is>
       </c>
-      <c r="AAY1" t="inlineStr">
+      <c r="ABI1" t="inlineStr">
         <is>
           <t>更新人</t>
         </is>
       </c>
-      <c r="AAZ1" t="inlineStr">
+      <c r="ABJ1" t="inlineStr">
         <is>
           <t>删除人</t>
         </is>
       </c>
-      <c r="ABA1" t="inlineStr">
+      <c r="ABK1" t="inlineStr">
         <is>
           <t>录入人</t>
         </is>
       </c>
-      <c r="ABB1" t="inlineStr">
+      <c r="ABL1" t="inlineStr">
         <is>
           <t>制单人</t>
         </is>
       </c>
-      <c r="ABC1" t="inlineStr">
+      <c r="ABM1" t="inlineStr">
         <is>
           <t>复核人</t>
         </is>
       </c>
-      <c r="ABD1" t="inlineStr">
+      <c r="ABN1" t="inlineStr">
         <is>
           <t>移交人</t>
         </is>
       </c>
-      <c r="ABE1" t="inlineStr">
+      <c r="ABO1" t="inlineStr">
         <is>
           <t>接收人</t>
         </is>
       </c>
-      <c r="ABF1" t="inlineStr">
+      <c r="ABP1" t="inlineStr">
         <is>
           <t>密级</t>
         </is>
       </c>
-      <c r="ABG1" t="inlineStr">
+      <c r="ABQ1" t="inlineStr">
         <is>
           <t>级别</t>
         </is>
       </c>
-      <c r="ABH1" t="inlineStr">
+      <c r="ABR1" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="ABI1" t="inlineStr">
+      <c r="ABS1" t="inlineStr">
         <is>
           <t>建制</t>
         </is>
       </c>
-      <c r="ABJ1" t="inlineStr">
+      <c r="ABT1" t="inlineStr">
         <is>
           <t>番号</t>
         </is>
       </c>
-      <c r="ABK1" t="inlineStr">
+      <c r="ABU1" t="inlineStr">
         <is>
           <t>部队</t>
         </is>
       </c>
-      <c r="ABL1" t="inlineStr">
+      <c r="ABV1" t="inlineStr">
         <is>
           <t>课目</t>
         </is>
       </c>
-      <c r="ABM1" t="inlineStr">
+      <c r="ABW1" t="inlineStr">
         <is>
           <t>驾驶员</t>
         </is>
       </c>
-      <c r="ABN1" t="inlineStr">
+      <c r="ABX1" t="inlineStr">
         <is>
           <t>附件</t>
         </is>
       </c>
-      <c r="ABO1" t="inlineStr">
+      <c r="ABY1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="ABP1" t="inlineStr">
+      <c r="ABZ1" t="inlineStr">
         <is>
           <t>标记</t>
         </is>
       </c>
-      <c r="ABQ1" t="inlineStr">
+      <c r="ACA1" t="inlineStr">
         <is>
           <t>网址</t>
         </is>
       </c>
-      <c r="ABR1" t="inlineStr">
+      <c r="ACB1" t="inlineStr">
         <is>
           <t>网站</t>
         </is>
       </c>
-      <c r="ABS1" t="inlineStr">
+      <c r="ACC1" t="inlineStr">
         <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="ABT1" t="inlineStr">
+      <c r="ACD1" t="inlineStr">
         <is>
           <t>超链接</t>
         </is>
       </c>
-      <c r="ABU1" t="inlineStr">
+      <c r="ACE1" t="inlineStr">
         <is>
           <t>路径</t>
         </is>
       </c>
-      <c r="ABV1" t="inlineStr">
+      <c r="ACF1" t="inlineStr">
         <is>
           <t>下载地址</t>
         </is>
       </c>
-      <c r="ABW1" t="inlineStr">
+      <c r="ACG1" t="inlineStr">
         <is>
           <t>访问地址</t>
         </is>
       </c>
-      <c r="ABX1" t="inlineStr">
+      <c r="ACH1" t="inlineStr">
         <is>
           <t>图片地址</t>
         </is>
       </c>
-      <c r="ABY1" t="inlineStr">
+      <c r="ACI1" t="inlineStr">
         <is>
           <t>附件地址</t>
         </is>
       </c>
-      <c r="ABZ1" t="inlineStr">
+      <c r="ACJ1" t="inlineStr">
         <is>
           <t>文件地址</t>
         </is>
       </c>
-      <c r="ACA1" t="inlineStr">
+      <c r="ACK1" t="inlineStr">
         <is>
           <t>主页</t>
         </is>
       </c>
-      <c r="ACB1" t="inlineStr">
+      <c r="ACL1" t="inlineStr">
         <is>
           <t>官网</t>
         </is>
       </c>
-      <c r="ACC1" t="inlineStr">
+      <c r="ACM1" t="inlineStr">
         <is>
           <t>域名</t>
         </is>
       </c>
-      <c r="ACD1" t="inlineStr">
+      <c r="ACN1" t="inlineStr">
         <is>
           <t>短链</t>
         </is>
       </c>
-      <c r="ACE1" t="inlineStr">
+      <c r="ACO1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="ACF1" t="inlineStr">
+      <c r="ACP1" t="inlineStr">
         <is>
           <t>amt</t>
         </is>
       </c>
-      <c r="ACG1" t="inlineStr">
+      <c r="ACQ1" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="ACH1" t="inlineStr">
+      <c r="ACR1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="ACI1" t="inlineStr">
+      <c r="ACS1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="ACJ1" t="inlineStr">
+      <c r="ACT1" t="inlineStr">
         <is>
           <t>fee</t>
         </is>
       </c>
-      <c r="ACK1" t="inlineStr">
+      <c r="ACU1" t="inlineStr">
         <is>
           <t>fees</t>
         </is>
       </c>
-      <c r="ACL1" t="inlineStr">
+      <c r="ACV1" t="inlineStr">
         <is>
           <t>salary</t>
         </is>
       </c>
-      <c r="ACM1" t="inlineStr">
+      <c r="ACW1" t="inlineStr">
         <is>
           <t>wage</t>
         </is>
       </c>
-      <c r="ACN1" t="inlineStr">
+      <c r="ACX1" t="inlineStr">
         <is>
           <t>wages</t>
         </is>
       </c>
-      <c r="ACO1" t="inlineStr">
+      <c r="ACY1" t="inlineStr">
         <is>
           <t>income</t>
         </is>
       </c>
-      <c r="ACP1" t="inlineStr">
+      <c r="ACZ1" t="inlineStr">
         <is>
           <t>expense</t>
         </is>
       </c>
-      <c r="ACQ1" t="inlineStr">
+      <c r="ADA1" t="inlineStr">
         <is>
           <t>expenses</t>
         </is>
       </c>
-      <c r="ACR1" t="inlineStr">
+      <c r="ADB1" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="ACS1" t="inlineStr">
+      <c r="ADC1" t="inlineStr">
         <is>
           <t>budget</t>
         </is>
       </c>
-      <c r="ACT1" t="inlineStr">
+      <c r="ADD1" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="ACU1" t="inlineStr">
+      <c r="ADE1" t="inlineStr">
         <is>
           <t>profit</t>
         </is>
       </c>
-      <c r="ACV1" t="inlineStr">
+      <c r="ADF1" t="inlineStr">
         <is>
           <t>payment</t>
         </is>
       </c>
-      <c r="ACW1" t="inlineStr">
+      <c r="ADG1" t="inlineStr">
         <is>
           <t>payable</t>
         </is>
       </c>
-      <c r="ACX1" t="inlineStr">
+      <c r="ADH1" t="inlineStr">
         <is>
           <t>receivable</t>
         </is>
       </c>
-      <c r="ACY1" t="inlineStr">
+      <c r="ADI1" t="inlineStr">
         <is>
           <t>charge</t>
         </is>
       </c>
-      <c r="ACZ1" t="inlineStr">
+      <c r="ADJ1" t="inlineStr">
         <is>
           <t>charges</t>
         </is>
       </c>
-      <c r="ADA1" t="inlineStr">
+      <c r="ADK1" t="inlineStr">
         <is>
           <t>fund</t>
         </is>
       </c>
-      <c r="ADB1" t="inlineStr">
+      <c r="ADL1" t="inlineStr">
         <is>
           <t>funds</t>
         </is>
       </c>
-      <c r="ADC1" t="inlineStr">
+      <c r="ADM1" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="ADD1" t="inlineStr">
+      <c r="ADN1" t="inlineStr">
         <is>
           <t>interest</t>
         </is>
       </c>
-      <c r="ADE1" t="inlineStr">
+      <c r="ADO1" t="inlineStr">
         <is>
           <t>capital</t>
         </is>
       </c>
-      <c r="ADF1" t="inlineStr">
+      <c r="ADP1" t="inlineStr">
         <is>
           <t>pay</t>
         </is>
       </c>
-      <c r="ADG1" t="inlineStr">
+      <c r="ADQ1" t="inlineStr">
         <is>
           <t>fare</t>
         </is>
       </c>
-      <c r="ADH1" t="inlineStr">
+      <c r="ADR1" t="inlineStr">
         <is>
           <t>toll</t>
         </is>
       </c>
-      <c r="ADI1" t="inlineStr">
+      <c r="ADS1" t="inlineStr">
         <is>
           <t>refund</t>
         </is>
       </c>
-      <c r="ADJ1" t="inlineStr">
+      <c r="ADT1" t="inlineStr">
         <is>
           <t>deposit</t>
         </is>
       </c>
-      <c r="ADK1" t="inlineStr">
+      <c r="ADU1" t="inlineStr">
         <is>
           <t>fine</t>
         </is>
       </c>
-      <c r="ADL1" t="inlineStr">
+      <c r="ADV1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="ADM1" t="inlineStr">
+      <c r="ADW1" t="inlineStr">
         <is>
           <t>royalty</t>
         </is>
       </c>
-      <c r="ADN1" t="inlineStr">
+      <c r="ADX1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>
       </c>
-      <c r="ADO1" t="inlineStr">
+      <c r="ADY1" t="inlineStr">
         <is>
           <t>dividend</t>
         </is>
       </c>
-      <c r="ADP1" t="inlineStr">
+      <c r="ADZ1" t="inlineStr">
         <is>
           <t>bonus</t>
         </is>
       </c>
-      <c r="ADQ1" t="inlineStr">
+      <c r="AEA1" t="inlineStr">
         <is>
           <t>subsidy</t>
         </is>
       </c>
-      <c r="ADR1" t="inlineStr">
+      <c r="AEB1" t="inlineStr">
         <is>
           <t>allowance</t>
         </is>
       </c>
-      <c r="ADS1" t="inlineStr">
+      <c r="AEC1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="ADT1" t="inlineStr">
+      <c r="AED1" t="inlineStr">
         <is>
           <t>earnings</t>
         </is>
       </c>
-      <c r="ADU1" t="inlineStr">
+      <c r="AEE1" t="inlineStr">
         <is>
           <t>turnover</t>
         </is>
       </c>
-      <c r="ADV1" t="inlineStr">
+      <c r="AEF1" t="inlineStr">
         <is>
           <t>rent</t>
         </is>
       </c>
-      <c r="ADW1" t="inlineStr">
+      <c r="AEG1" t="inlineStr">
         <is>
           <t>loan</t>
         </is>
       </c>
-      <c r="ADX1" t="inlineStr">
+      <c r="AEH1" t="inlineStr">
         <is>
           <t>mortgage</t>
         </is>
       </c>
-      <c r="ADY1" t="inlineStr">
+      <c r="AEI1" t="inlineStr">
         <is>
           <t>arrears</t>
         </is>
       </c>
-      <c r="ADZ1" t="inlineStr">
+      <c r="AEJ1" t="inlineStr">
         <is>
           <t>receipt</t>
         </is>
       </c>
-      <c r="AEA1" t="inlineStr">
+      <c r="AEK1" t="inlineStr">
         <is>
           <t>receipts</t>
         </is>
       </c>
-      <c r="AEB1" t="inlineStr">
+      <c r="AEL1" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="AEC1" t="inlineStr">
+      <c r="AEM1" t="inlineStr">
         <is>
           <t>disbursement</t>
         </is>
       </c>
-      <c r="AED1" t="inlineStr">
+      <c r="AEN1" t="inlineStr">
         <is>
           <t>expenditure</t>
         </is>
       </c>
-      <c r="AEE1" t="inlineStr">
+      <c r="AEO1" t="inlineStr">
         <is>
           <t>spending</t>
         </is>
       </c>
-      <c r="AEF1" t="inlineStr">
+      <c r="AEP1" t="inlineStr">
         <is>
           <t>worth</t>
         </is>
       </c>
-      <c r="AEG1" t="inlineStr">
+      <c r="AEQ1" t="inlineStr">
         <is>
           <t>valuation</t>
         </is>
       </c>
-      <c r="AEH1" t="inlineStr">
+      <c r="AER1" t="inlineStr">
         <is>
           <t>equity</t>
         </is>
       </c>
-      <c r="AEI1" t="inlineStr">
+      <c r="AES1" t="inlineStr">
         <is>
           <t>dues</t>
         </is>
       </c>
-      <c r="AEJ1" t="inlineStr">
+      <c r="AET1" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="AEK1" t="inlineStr">
+      <c r="AEU1" t="inlineStr">
         <is>
           <t>installment</t>
         </is>
       </c>
-      <c r="AEL1" t="inlineStr">
+      <c r="AEV1" t="inlineStr">
         <is>
           <t>prepayment</t>
         </is>
       </c>
-      <c r="AEM1" t="inlineStr">
+      <c r="AEW1" t="inlineStr">
         <is>
           <t>deductible</t>
         </is>
       </c>
-      <c r="AEN1" t="inlineStr">
+      <c r="AEX1" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AEO1" t="inlineStr">
+      <c r="AEY1" t="inlineStr">
         <is>
           <t>premium</t>
         </is>
       </c>
-      <c r="AEP1" t="inlineStr">
+      <c r="AEZ1" t="inlineStr">
         <is>
           <t>reimbursement</t>
         </is>
       </c>
-      <c r="AEQ1" t="inlineStr">
+      <c r="AFA1" t="inlineStr">
         <is>
           <t>stipend</t>
         </is>
       </c>
-      <c r="AER1" t="inlineStr">
+      <c r="AFB1" t="inlineStr">
         <is>
           <t>honorarium</t>
         </is>
       </c>
-      <c r="AES1" t="inlineStr">
+      <c r="AFC1" t="inlineStr">
         <is>
           <t>gratuity</t>
         </is>
       </c>
-      <c r="AET1" t="inlineStr">
+      <c r="AFD1" t="inlineStr">
         <is>
           <t>payout</t>
         </is>
       </c>
-      <c r="AEU1" t="inlineStr">
+      <c r="AFE1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="AEV1" t="inlineStr">
+      <c r="AFF1" t="inlineStr">
         <is>
           <t>views</t>
         </is>
       </c>
-      <c r="AEW1" t="inlineStr">
+      <c r="AFG1" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
       </c>
-      <c r="AEX1" t="inlineStr">
+      <c r="AFH1" t="inlineStr">
         <is>
           <t>clicks</t>
         </is>
       </c>
-      <c r="AEY1" t="inlineStr">
+      <c r="AFI1" t="inlineStr">
         <is>
           <t>downloads</t>
         </is>
       </c>
-      <c r="AEZ1" t="inlineStr">
+      <c r="AFJ1" t="inlineStr">
         <is>
           <t>plays</t>
         </is>
       </c>
-      <c r="AFA1" t="inlineStr">
+      <c r="AFK1" t="inlineStr">
         <is>
           <t>impressions</t>
         </is>
       </c>
-      <c r="AFB1" t="inlineStr">
+      <c r="AFL1" t="inlineStr">
         <is>
           <t>pageviews</t>
         </is>
       </c>
-      <c r="AFC1" t="inlineStr">
+      <c r="AFM1" t="inlineStr">
         <is>
           <t>followers</t>
         </is>
       </c>
-      <c r="AFD1" t="inlineStr">
+      <c r="AFN1" t="inlineStr">
         <is>
           <t>fans</t>
         </is>
       </c>
-      <c r="AFE1" t="inlineStr">
+      <c r="AFO1" t="inlineStr">
         <is>
           <t>likes</t>
         </is>
       </c>
-      <c r="AFF1" t="inlineStr">
+      <c r="AFP1" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="AFG1" t="inlineStr">
+      <c r="AFQ1" t="inlineStr">
         <is>
           <t>shares</t>
         </is>
       </c>
-      <c r="AFH1" t="inlineStr">
+      <c r="AFR1" t="inlineStr">
         <is>
           <t>is</t>
         </is>
       </c>
-      <c r="AFI1" t="inlineStr">
+      <c r="AFS1" t="inlineStr">
         <is>
           <t>has</t>
         </is>
       </c>
-      <c r="AFJ1" t="inlineStr">
+      <c r="AFT1" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="AFK1" t="inlineStr">
+      <c r="AFU1" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="AFL1" t="inlineStr">
+      <c r="AFV1" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
       </c>
-      <c r="AFM1" t="inlineStr">
+      <c r="AFW1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="AFN1" t="inlineStr">
+      <c r="AFX1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AFO1" t="inlineStr">
+      <c r="AFY1" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="AFP1" t="inlineStr">
+      <c r="AFZ1" t="inlineStr">
         <is>
           <t>deleted</t>
         </is>
       </c>
-      <c r="AFQ1" t="inlineStr">
+      <c r="AGA1" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="AFR1" t="inlineStr">
+      <c r="AGB1" t="inlineStr">
         <is>
           <t>yn</t>
         </is>
       </c>
-      <c r="AFS1" t="inlineStr">
+      <c r="AGC1" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="AFT1" t="inlineStr">
+      <c r="AGD1" t="inlineStr">
         <is>
           <t>allowed</t>
         </is>
       </c>
-      <c r="AFU1" t="inlineStr">
+      <c r="AGE1" t="inlineStr">
         <is>
           <t>need</t>
         </is>
       </c>
-      <c r="AFV1" t="inlineStr">
+      <c r="AGF1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="AFW1" t="inlineStr">
+      <c r="AGG1" t="inlineStr">
         <is>
           <t>checked</t>
         </is>
       </c>
-      <c r="AFX1" t="inlineStr">
+      <c r="AGH1" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="AFY1" t="inlineStr">
+      <c r="AGI1" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="AFZ1" t="inlineStr">
+      <c r="AGJ1" t="inlineStr">
         <is>
           <t>locked</t>
         </is>
       </c>
-      <c r="AGA1" t="inlineStr">
+      <c r="AGK1" t="inlineStr">
         <is>
           <t>visible</t>
         </is>
       </c>
-      <c r="AGB1" t="inlineStr">
+      <c r="AGL1" t="inlineStr">
         <is>
           <t>available</t>
         </is>
       </c>
-      <c r="AGC1" t="inlineStr">
+      <c r="AGM1" t="inlineStr">
         <is>
           <t>permitted</t>
         </is>
       </c>
-      <c r="AGD1" t="inlineStr">
+      <c r="AGN1" t="inlineStr">
         <is>
           <t>yesno</t>
         </is>
       </c>
-      <c r="AGE1" t="inlineStr">
+      <c r="AGO1" t="inlineStr">
         <is>
           <t>truefalse</t>
         </is>
       </c>
-      <c r="AGF1" t="inlineStr">
+      <c r="AGP1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="AGG1" t="inlineStr">
+      <c r="AGQ1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="AGH1" t="inlineStr">
+      <c r="AGR1" t="inlineStr">
         <is>
           <t>quarter</t>
         </is>
       </c>
-      <c r="AGI1" t="inlineStr">
+      <c r="AGS1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="AGJ1" t="inlineStr">
+      <c r="AGT1" t="inlineStr">
         <is>
           <t>hour</t>
         </is>
       </c>
-      <c r="AGK1" t="inlineStr">
+      <c r="AGU1" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="AGL1" t="inlineStr">
+      <c r="AGV1" t="inlineStr">
         <is>
           <t>second</t>
         </is>
       </c>
-      <c r="AGM1" t="inlineStr">
+      <c r="AGW1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="AGN1" t="inlineStr">
+      <c r="AGX1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="AGO1" t="inlineStr">
+      <c r="AGY1" t="inlineStr">
         <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="AGP1" t="inlineStr">
+      <c r="AGZ1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="AGQ1" t="inlineStr">
+      <c r="AHA1" t="inlineStr">
         <is>
           <t>lon</t>
         </is>
       </c>
-      <c r="AGR1" t="inlineStr">
+      <c r="AHB1" t="inlineStr">
         <is>
           <t>coord</t>
         </is>
       </c>
-      <c r="AGS1" t="inlineStr">
+      <c r="AHC1" t="inlineStr">
         <is>
           <t>coords</t>
         </is>
       </c>
-      <c r="AGT1" t="inlineStr">
+      <c r="AHD1" t="inlineStr">
         <is>
           <t>coordinate</t>
         </is>
       </c>
-      <c r="AGU1" t="inlineStr">
+      <c r="AHE1" t="inlineStr">
         <is>
           <t>gps</t>
         </is>
       </c>
-      <c r="AGV1" t="inlineStr">
+      <c r="AHF1" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="AGW1" t="inlineStr">
+      <c r="AHG1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="AGX1" t="inlineStr">
+      <c r="AHH1" t="inlineStr">
         <is>
           <t>dt</t>
         </is>
       </c>
-      <c r="AGY1" t="inlineStr">
+      <c r="AHI1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="AGZ1" t="inlineStr">
+      <c r="AHJ1" t="inlineStr">
         <is>
           <t>elapsed</t>
         </is>
       </c>
-      <c r="AHA1" t="inlineStr">
+      <c r="AHK1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="AHB1" t="inlineStr">
+      <c r="AHL1" t="inlineStr">
         <is>
           <t>latency</t>
         </is>
       </c>
-      <c r="AHC1" t="inlineStr">
+      <c r="AHM1" t="inlineStr">
         <is>
           <t>qty</t>
         </is>
       </c>
-      <c r="AHD1" t="inlineStr">
+      <c r="AHN1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="AHE1" t="inlineStr">
+      <c r="AHO1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AHF1" t="inlineStr">
+      <c r="AHP1" t="inlineStr">
         <is>
           <t>cnt</t>
         </is>
       </c>
-      <c r="AHG1" t="inlineStr">
+      <c r="AHQ1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="AHH1" t="inlineStr">
+      <c r="AHR1" t="inlineStr">
         <is>
           <t>members</t>
         </is>
       </c>
-      <c r="AHI1" t="inlineStr">
+      <c r="AHS1" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="AHJ1" t="inlineStr">
+      <c r="AHT1" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
-      <c r="AHK1" t="inlineStr">
+      <c r="AHU1" t="inlineStr">
         <is>
           <t>pieces</t>
         </is>
       </c>
-      <c r="AHL1" t="inlineStr">
+      <c r="AHV1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="AHM1" t="inlineStr">
+      <c r="AHW1" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="AHN1" t="inlineStr">
+      <c r="AHX1" t="inlineStr">
         <is>
           <t>height</t>
         </is>
       </c>
-      <c r="AHO1" t="inlineStr">
+      <c r="AHY1" t="inlineStr">
         <is>
           <t>thickness</t>
         </is>
       </c>
-      <c r="AHP1" t="inlineStr">
+      <c r="AHZ1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AHQ1" t="inlineStr">
+      <c r="AIA1" t="inlineStr">
         <is>
           <t>distance</t>
         </is>
       </c>
-      <c r="AHR1" t="inlineStr">
+      <c r="AIB1" t="inlineStr">
         <is>
           <t>mileage</t>
         </is>
       </c>
-      <c r="AHS1" t="inlineStr">
+      <c r="AIC1" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="AHT1" t="inlineStr">
+      <c r="AID1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AHU1" t="inlineStr">
+      <c r="AIE1" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="AHV1" t="inlineStr">
+      <c r="AIF1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="AHW1" t="inlineStr">
+      <c r="AIG1" t="inlineStr">
         <is>
           <t>temperature</t>
         </is>
       </c>
-      <c r="AHX1" t="inlineStr">
+      <c r="AIH1" t="inlineStr">
         <is>
           <t>humidity</t>
         </is>
       </c>
-      <c r="AHY1" t="inlineStr">
+      <c r="AII1" t="inlineStr">
         <is>
           <t>density</t>
         </is>
       </c>
-      <c r="AHZ1" t="inlineStr">
+      <c r="AIJ1" t="inlineStr">
         <is>
           <t>pressure</t>
         </is>
       </c>
-      <c r="AIA1" t="inlineStr">
+      <c r="AIK1" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="AIB1" t="inlineStr">
+      <c r="AIL1" t="inlineStr">
         <is>
           <t>flow</t>
         </is>
       </c>
-      <c r="AIC1" t="inlineStr">
+      <c r="AIM1" t="inlineStr">
         <is>
           <t>power</t>
         </is>
       </c>
-      <c r="AID1" t="inlineStr">
+      <c r="AIN1" t="inlineStr">
         <is>
           <t>voltage</t>
         </is>
       </c>
-      <c r="AIE1" t="inlineStr">
+      <c r="AIO1" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="AIF1" t="inlineStr">
+      <c r="AIP1" t="inlineStr">
         <is>
           <t>elevation</t>
         </is>
       </c>
-      <c r="AIG1" t="inlineStr">
+      <c r="AIQ1" t="inlineStr">
         <is>
           <t>altitude</t>
         </is>
       </c>
-      <c r="AIH1" t="inlineStr">
+      <c r="AIR1" t="inlineStr">
         <is>
           <t>diameter</t>
         </is>
       </c>
-      <c r="AII1" t="inlineStr">
+      <c r="AIS1" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="AIJ1" t="inlineStr">
+      <c r="AIT1" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="AIK1" t="inlineStr">
+      <c r="AIU1" t="inlineStr">
         <is>
           <t>span</t>
         </is>
       </c>
-      <c r="AIL1" t="inlineStr">
+      <c r="AIV1" t="inlineStr">
         <is>
           <t>spacing</t>
         </is>
       </c>
-      <c r="AIM1" t="inlineStr">
+      <c r="AIW1" t="inlineStr">
         <is>
           <t>slope</t>
         </is>
       </c>
-      <c r="AIN1" t="inlineStr">
+      <c r="AIX1" t="inlineStr">
         <is>
           <t>hardness</t>
         </is>
       </c>
-      <c r="AIO1" t="inlineStr">
+      <c r="AIY1" t="inlineStr">
         <is>
           <t>strength</t>
         </is>
       </c>
-      <c r="AIP1" t="inlineStr">
+      <c r="AIZ1" t="inlineStr">
         <is>
           <t>stress</t>
         </is>
       </c>
-      <c r="AIQ1" t="inlineStr">
+      <c r="AJA1" t="inlineStr">
         <is>
           <t>strain</t>
         </is>
       </c>
-      <c r="AIR1" t="inlineStr">
+      <c r="AJB1" t="inlineStr">
         <is>
           <t>modulus</t>
         </is>
       </c>
-      <c r="AIS1" t="inlineStr">
+      <c r="AJC1" t="inlineStr">
         <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="AIT1" t="inlineStr">
+      <c r="AJD1" t="inlineStr">
         <is>
           <t>capacitance</t>
         </is>
       </c>
-      <c r="AIU1" t="inlineStr">
+      <c r="AJE1" t="inlineStr">
         <is>
           <t>inductance</t>
         </is>
       </c>
-      <c r="AIV1" t="inlineStr">
+      <c r="AJF1" t="inlineStr">
         <is>
           <t>impedance</t>
         </is>
       </c>
-      <c r="AIW1" t="inlineStr">
+      <c r="AJG1" t="inlineStr">
         <is>
           <t>consumption</t>
         </is>
       </c>
-      <c r="AIX1" t="inlineStr">
+      <c r="AJH1" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="AIY1" t="inlineStr">
+      <c r="AJI1" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="AIZ1" t="inlineStr">
+      <c r="AJJ1" t="inlineStr">
         <is>
           <t>velocity</t>
         </is>
       </c>
-      <c r="AJA1" t="inlineStr">
+      <c r="AJK1" t="inlineStr">
         <is>
           <t>torque</t>
         </is>
       </c>
-      <c r="AJB1" t="inlineStr">
+      <c r="AJL1" t="inlineStr">
         <is>
           <t>brightness</t>
         </is>
       </c>
-      <c r="AJC1" t="inlineStr">
+      <c r="AJM1" t="inlineStr">
         <is>
           <t>amplitude</t>
         </is>
       </c>
-      <c r="AJD1" t="inlineStr">
+      <c r="AJN1" t="inlineStr">
         <is>
           <t>deflection</t>
         </is>
       </c>
-      <c r="AJE1" t="inlineStr">
+      <c r="AJO1" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AJF1" t="inlineStr">
+      <c r="AJP1" t="inlineStr">
         <is>
           <t>displacement</t>
         </is>
       </c>
-      <c r="AJG1" t="inlineStr">
+      <c r="AJQ1" t="inlineStr">
         <is>
           <t>noise</t>
         </is>
       </c>
-      <c r="AJH1" t="inlineStr">
+      <c r="AJR1" t="inlineStr">
         <is>
           <t>decibel</t>
         </is>
       </c>
-      <c r="AJI1" t="inlineStr">
+      <c r="AJS1" t="inlineStr">
         <is>
           <t>radiation</t>
         </is>
       </c>
-      <c r="AJJ1" t="inlineStr">
+      <c r="AJT1" t="inlineStr">
         <is>
           <t>clearance</t>
         </is>
       </c>
-      <c r="AJK1" t="inlineStr">
+      <c r="AJU1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="AJL1" t="inlineStr">
+      <c r="AJV1" t="inlineStr">
         <is>
           <t>ranking</t>
         </is>
       </c>
-      <c r="AJM1" t="inlineStr">
+      <c r="AJW1" t="inlineStr">
         <is>
           <t>sort</t>
         </is>
       </c>
-      <c r="AJN1" t="inlineStr">
+      <c r="AJX1" t="inlineStr">
         <is>
           <t>seq</t>
         </is>
       </c>
-      <c r="AJO1" t="inlineStr">
+      <c r="AJY1" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="AJP1" t="inlineStr">
+      <c r="AJZ1" t="inlineStr">
         <is>
           <t>serial</t>
         </is>
       </c>
-      <c r="AJQ1" t="inlineStr">
+      <c r="AKA1" t="inlineStr">
         <is>
           <t>page</t>
         </is>
       </c>
-      <c r="AJR1" t="inlineStr">
+      <c r="AKB1" t="inlineStr">
         <is>
           <t>pages</t>
         </is>
       </c>
-      <c r="AJS1" t="inlineStr">
+      <c r="AKC1" t="inlineStr">
         <is>
           <t>floor</t>
         </is>
       </c>
-      <c r="AJT1" t="inlineStr">
+      <c r="AKD1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="AJU1" t="inlineStr">
+      <c r="AKE1" t="inlineStr">
         <is>
           <t>ordinal</t>
         </is>
       </c>
-      <c r="AJV1" t="inlineStr">
+      <c r="AKF1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="AJW1" t="inlineStr">
+      <c r="AKG1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="AJX1" t="inlineStr">
+      <c r="AKH1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="AJY1" t="inlineStr">
+      <c r="AKI1" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="AJZ1" t="inlineStr">
+      <c r="AKJ1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
       </c>
-      <c r="AKA1" t="inlineStr">
+      <c r="AKK1" t="inlineStr">
         <is>
           <t>coefficient</t>
         </is>
       </c>
-      <c r="AKB1" t="inlineStr">
+      <c r="AKL1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="AKC1" t="inlineStr">
+      <c r="AKM1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AKD1" t="inlineStr">
+      <c r="AKN1" t="inlineStr">
         <is>
           <t>discount</t>
         </is>
       </c>
-      <c r="AKE1" t="inlineStr">
+      <c r="AKO1" t="inlineStr">
         <is>
           <t>proportion</t>
         </is>
       </c>
-      <c r="AKF1" t="inlineStr">
+      <c r="AKP1" t="inlineStr">
         <is>
           <t>probability</t>
         </is>
       </c>
-      <c r="AKG1" t="inlineStr">
+      <c r="AKQ1" t="inlineStr">
         <is>
           <t>likelihood</t>
         </is>
       </c>
-      <c r="AKH1" t="inlineStr">
+      <c r="AKR1" t="inlineStr">
         <is>
           <t>permille</t>
         </is>
       </c>
-      <c r="AKI1" t="inlineStr">
+      <c r="AKS1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AKJ1" t="inlineStr">
+      <c r="AKT1" t="inlineStr">
         <is>
           <t>gpa</t>
         </is>
       </c>
-      <c r="AKK1" t="inlineStr">
+      <c r="AKU1" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="AKL1" t="inlineStr">
+      <c r="AKV1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="AKM1" t="inlineStr">
+      <c r="AKW1" t="inlineStr">
         <is>
           <t>ratings</t>
         </is>
       </c>
-      <c r="AKN1" t="inlineStr">
+      <c r="AKX1" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="AKO1" t="inlineStr">
+      <c r="AKY1" t="inlineStr">
         <is>
           <t>totals</t>
         </is>
       </c>
-      <c r="AKP1" t="inlineStr">
+      <c r="AKZ1" t="inlineStr">
         <is>
           <t>subtotal</t>
         </is>
       </c>
-      <c r="AKQ1" t="inlineStr">
+      <c r="ALA1" t="inlineStr">
         <is>
           <t>subtotals</t>
         </is>
       </c>
-      <c r="AKR1" t="inlineStr">
+      <c r="ALB1" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="AKS1" t="inlineStr">
+      <c r="ALC1" t="inlineStr">
         <is>
           <t>sums</t>
         </is>
       </c>
-      <c r="AKT1" t="inlineStr">
+      <c r="ALD1" t="inlineStr">
         <is>
           <t>aggregate</t>
         </is>
       </c>
-      <c r="AKU1" t="inlineStr">
+      <c r="ALE1" t="inlineStr">
         <is>
           <t>aggregates</t>
         </is>
       </c>
-      <c r="AKV1" t="inlineStr">
+      <c r="ALF1" t="inlineStr">
         <is>
           <t>cumulative</t>
         </is>
       </c>
-      <c r="AKW1" t="inlineStr">
+      <c r="ALG1" t="inlineStr">
         <is>
           <t>accumulation</t>
         </is>
       </c>
-      <c r="AKX1" t="inlineStr">
+      <c r="ALH1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
-      <c r="AKY1" t="inlineStr">
+      <c r="ALI1" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="AKZ1" t="inlineStr">
+      <c r="ALJ1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="ALA1" t="inlineStr">
+      <c r="ALK1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="ALB1" t="inlineStr">
+      <c r="ALL1" t="inlineStr">
         <is>
           <t>memo</t>
         </is>
       </c>
-      <c r="ALC1" t="inlineStr">
+      <c r="ALM1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="ALD1" t="inlineStr">
+      <c r="ALN1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="ALE1" t="inlineStr">
+      <c r="ALO1" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="ALF1" t="inlineStr">
+      <c r="ALP1" t="inlineStr">
         <is>
           <t>details</t>
         </is>
       </c>
-      <c r="ALG1" t="inlineStr">
+      <c r="ALQ1" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
-      <c r="ALH1" t="inlineStr">
+      <c r="ALR1" t="inlineStr">
         <is>
           <t>contents</t>
         </is>
       </c>
-      <c r="ALI1" t="inlineStr">
+      <c r="ALS1" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="ALJ1" t="inlineStr">
+      <c r="ALT1" t="inlineStr">
         <is>
           <t>abstract</t>
         </is>
       </c>
-      <c r="ALK1" t="inlineStr">
+      <c r="ALU1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="ALL1" t="inlineStr">
+      <c r="ALV1" t="inlineStr">
         <is>
           <t>feedback</t>
         </is>
       </c>
-      <c r="ALM1" t="inlineStr">
+      <c r="ALW1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="ALN1" t="inlineStr">
+      <c r="ALX1" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="ALO1" t="inlineStr">
+      <c r="ALY1" t="inlineStr">
         <is>
           <t>intro</t>
         </is>
       </c>
-      <c r="ALP1" t="inlineStr">
+      <c r="ALZ1" t="inlineStr">
         <is>
           <t>introduction</t>
         </is>
       </c>
-      <c r="ALQ1" t="inlineStr">
+      <c r="AMA1" t="inlineStr">
         <is>
           <t>overview</t>
         </is>
       </c>
-      <c r="ALR1" t="inlineStr">
+      <c r="AMB1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
       </c>
-      <c r="ALS1" t="inlineStr">
+      <c r="AMC1" t="inlineStr">
         <is>
           <t>suggestion</t>
         </is>
       </c>
-      <c r="ALT1" t="inlineStr">
+      <c r="AMD1" t="inlineStr">
         <is>
           <t>suggestions</t>
         </is>
       </c>
-      <c r="ALU1" t="inlineStr">
+      <c r="AME1" t="inlineStr">
         <is>
           <t>requirement</t>
         </is>
       </c>
-      <c r="ALV1" t="inlineStr">
+      <c r="AMF1" t="inlineStr">
         <is>
           <t>requirements</t>
         </is>
       </c>
-      <c r="ALW1" t="inlineStr">
+      <c r="AMG1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="ALX1" t="inlineStr">
+      <c r="AMH1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="ALY1" t="inlineStr">
+      <c r="AMI1" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="ALZ1" t="inlineStr">
+      <c r="AMJ1" t="inlineStr">
         <is>
           <t>advantage</t>
         </is>
       </c>
-      <c r="AMA1" t="inlineStr">
+      <c r="AMK1" t="inlineStr">
         <is>
           <t>advantages</t>
         </is>
       </c>
-      <c r="AMB1" t="inlineStr">
+      <c r="AML1" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="AMC1" t="inlineStr">
+      <c r="AMM1" t="inlineStr">
         <is>
           <t>messages</t>
         </is>
       </c>
-      <c r="AMD1" t="inlineStr">
+      <c r="AMN1" t="inlineStr">
         <is>
           <t>statement</t>
         </is>
       </c>
-      <c r="AME1" t="inlineStr">
+      <c r="AMO1" t="inlineStr">
         <is>
           <t>statements</t>
         </is>
       </c>
-      <c r="AMF1" t="inlineStr">
+      <c r="AMP1" t="inlineStr">
         <is>
           <t>annotation</t>
         </is>
       </c>
-      <c r="AMG1" t="inlineStr">
+      <c r="AMQ1" t="inlineStr">
         <is>
           <t>annotations</t>
         </is>
       </c>
-      <c r="AMH1" t="inlineStr">
+      <c r="AMR1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="AMI1" t="inlineStr">
+      <c r="AMS1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="AMJ1" t="inlineStr">
+      <c r="AMT1" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="AMK1" t="inlineStr">
+      <c r="AMU1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AML1" t="inlineStr">
+      <c r="AMV1" t="inlineStr">
         <is>
           <t>names</t>
         </is>
       </c>
-      <c r="AMM1" t="inlineStr">
+      <c r="AMW1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AMN1" t="inlineStr">
+      <c r="AMX1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="AMO1" t="inlineStr">
+      <c r="AMY1" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="AMP1" t="inlineStr">
+      <c r="AMZ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AMQ1" t="inlineStr">
+      <c r="ANA1" t="inlineStr">
         <is>
           <t>types</t>
         </is>
       </c>
-      <c r="AMR1" t="inlineStr">
+      <c r="ANB1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="AMS1" t="inlineStr">
+      <c r="ANC1" t="inlineStr">
         <is>
           <t>kinds</t>
         </is>
       </c>
-      <c r="AMT1" t="inlineStr">
+      <c r="AND1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="AMU1" t="inlineStr">
+      <c r="ANE1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="AMV1" t="inlineStr">
+      <c r="ANF1" t="inlineStr">
         <is>
           <t>spec</t>
         </is>
       </c>
-      <c r="AMW1" t="inlineStr">
+      <c r="ANG1" t="inlineStr">
         <is>
           <t>specs</t>
         </is>
       </c>
-      <c r="AMX1" t="inlineStr">
+      <c r="ANH1" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="AMY1" t="inlineStr">
+      <c r="ANI1" t="inlineStr">
         <is>
           <t>color</t>
         </is>
       </c>
-      <c r="AMZ1" t="inlineStr">
+      <c r="ANJ1" t="inlineStr">
         <is>
           <t>colour</t>
         </is>
       </c>
-      <c r="ANA1" t="inlineStr">
+      <c r="ANK1" t="inlineStr">
         <is>
           <t>dept</t>
         </is>
       </c>
-      <c r="ANB1" t="inlineStr">
+      <c r="ANL1" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="ANC1" t="inlineStr">
+      <c r="ANM1" t="inlineStr">
         <is>
           <t>organization</t>
         </is>
       </c>
-      <c r="AND1" t="inlineStr">
+      <c r="ANN1" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="ANE1" t="inlineStr">
+      <c r="ANO1" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="ANF1" t="inlineStr">
+      <c r="ANP1" t="inlineStr">
         <is>
           <t>school</t>
         </is>
       </c>
-      <c r="ANG1" t="inlineStr">
+      <c r="ANQ1" t="inlineStr">
         <is>
           <t>hospital</t>
         </is>
       </c>
-      <c r="ANH1" t="inlineStr">
+      <c r="ANR1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="ANI1" t="inlineStr">
+      <c r="ANS1" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
       </c>
-      <c r="ANJ1" t="inlineStr">
+      <c r="ANT1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="ANK1" t="inlineStr">
+      <c r="ANU1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="ANL1" t="inlineStr">
+      <c r="ANV1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="ANM1" t="inlineStr">
+      <c r="ANW1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="ANN1" t="inlineStr">
+      <c r="ANX1" t="inlineStr">
         <is>
           <t>labels</t>
         </is>
       </c>
-      <c r="ANO1" t="inlineStr">
+      <c r="ANY1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="ANP1" t="inlineStr">
+      <c r="ANZ1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="ANQ1" t="inlineStr">
+      <c r="AOA1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="ANR1" t="inlineStr">
+      <c r="AOB1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="ANS1" t="inlineStr">
+      <c r="AOC1" t="inlineStr">
         <is>
           <t>occupation</t>
         </is>
       </c>
-      <c r="ANT1" t="inlineStr">
+      <c r="AOD1" t="inlineStr">
         <is>
           <t>position</t>
         </is>
       </c>
-      <c r="ANU1" t="inlineStr">
+      <c r="AOE1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="ANV1" t="inlineStr">
+      <c r="AOF1" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="ANW1" t="inlineStr">
+      <c r="AOG1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="ANX1" t="inlineStr">
+      <c r="AOH1" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="ANY1" t="inlineStr">
+      <c r="AOI1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="ANZ1" t="inlineStr">
+      <c r="AOJ1" t="inlineStr">
         <is>
           <t>uri</t>
         </is>
       </c>
-      <c r="AOA1" t="inlineStr">
+      <c r="AOK1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="AOB1" t="inlineStr">
+      <c r="AOL1" t="inlineStr">
         <is>
           <t>links</t>
         </is>
       </c>
-      <c r="AOC1" t="inlineStr">
+      <c r="AOM1" t="inlineStr">
         <is>
           <t>href</t>
         </is>
       </c>
-      <c r="AOD1" t="inlineStr">
+      <c r="AON1" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="AOE1" t="inlineStr">
+      <c r="AOO1" t="inlineStr">
         <is>
           <t>paths</t>
         </is>
       </c>
-      <c r="AOF1" t="inlineStr">
+      <c r="AOP1" t="inlineStr">
         <is>
           <t>permalink</t>
         </is>
       </c>
-      <c r="AOG1" t="inlineStr">
+      <c r="AOQ1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="AOH1" t="inlineStr">
+      <c r="AOR1" t="inlineStr">
         <is>
           <t>homepage</t>
         </is>
       </c>
-      <c r="AOI1" t="inlineStr">
+      <c r="AOS1" t="inlineStr">
         <is>
           <t>share</t>
         </is>
